--- a/reports/Total_Test_Cases_Report.xlsx
+++ b/reports/Total_Test_Cases_Report.xlsx
@@ -547,7 +547,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B13">
-        <v>133238</v>
+        <v>16459</v>
       </c>
     </row>
     <row r="14">
@@ -563,7 +563,7 @@
         <v>Requests Per Second (RPS)</v>
       </c>
       <c r="B15">
-        <v>2220.63</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="16">
@@ -571,7 +571,7 @@
         <v>Average Latency (ms)</v>
       </c>
       <c r="B16">
-        <v>45.04</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="17">
@@ -579,7 +579,7 @@
         <v>Maximum Latency (ms)</v>
       </c>
       <c r="B17">
-        <v>251</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="19">
@@ -600,7 +600,7 @@
         <v>Report Consolidated Time</v>
       </c>
       <c r="B21" t="str">
-        <v>8/8/2026, 12:33:28 pm</v>
+        <v>8/8/2026, 12:44:27 pm</v>
       </c>
     </row>
     <row r="22">
@@ -669,13 +669,13 @@
         <v>FAIL</v>
       </c>
       <c r="D2" t="str">
-        <v>1.51 sec</v>
+        <v>4.82 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-03T18:43:51.179Z</v>
+        <v>2026-08-08T07:05:29.938Z</v>
       </c>
       <c r="F2" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         <v>FAIL</v>
       </c>
       <c r="D3" t="str">
-        <v>0.83 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-03T18:43:52.012Z</v>
+        <v>2026-08-08T07:05:33.836Z</v>
       </c>
       <c r="F3" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="4">
@@ -709,13 +709,13 @@
         <v>FAIL</v>
       </c>
       <c r="D4" t="str">
-        <v>0.81 sec</v>
+        <v>4.29 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-03T18:43:52.827Z</v>
+        <v>2026-08-08T07:05:38.124Z</v>
       </c>
       <c r="F4" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="5">
@@ -729,10 +729,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>3.75 sec</v>
+        <v>3.79 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-03T18:43:56.580Z</v>
+        <v>2026-08-08T07:05:41.915Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -749,10 +749,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>3.59 sec</v>
+        <v>3.91 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-03T18:44:00.175Z</v>
+        <v>2026-08-08T07:05:45.827Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -769,10 +769,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>3.55 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-03T18:44:03.728Z</v>
+        <v>2026-08-08T07:05:49.726Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -789,13 +789,13 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.21 sec</v>
+        <v>4.15 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-03T18:44:04.938Z</v>
+        <v>2026-08-08T07:05:53.875Z</v>
       </c>
       <c r="F8" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="9">
@@ -809,10 +809,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>3.70 sec</v>
+        <v>3.81 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-03T18:44:08.642Z</v>
+        <v>2026-08-08T07:05:57.686Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -829,10 +829,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>3.73 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-03T18:44:12.369Z</v>
+        <v>2026-08-08T07:06:01.588Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -849,13 +849,13 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>1.31 sec</v>
+        <v>3.92 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-03T18:44:13.678Z</v>
+        <v>2026-08-08T07:06:05.510Z</v>
       </c>
       <c r="F11" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="12">
@@ -869,13 +869,13 @@
         <v>PASS</v>
       </c>
       <c r="D12" t="str">
-        <v>1.14 sec</v>
+        <v>3.73 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-03T18:44:14.815Z</v>
+        <v>2026-08-08T07:06:09.237Z</v>
       </c>
       <c r="F12" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="13">
@@ -889,13 +889,13 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>1.61 sec</v>
+        <v>4.05 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-03T18:44:16.422Z</v>
+        <v>2026-08-08T07:06:13.291Z</v>
       </c>
       <c r="F13" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="14">
@@ -909,13 +909,13 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.99 sec</v>
+        <v>3.77 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-03T18:44:17.409Z</v>
+        <v>2026-08-08T07:06:17.063Z</v>
       </c>
       <c r="F14" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="15">
@@ -929,13 +929,13 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>1.07 sec</v>
+        <v>4.08 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-03T18:44:18.483Z</v>
+        <v>2026-08-08T07:06:21.142Z</v>
       </c>
       <c r="F15" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="16">
@@ -949,13 +949,13 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.99 sec</v>
+        <v>3.96 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-03T18:44:19.478Z</v>
+        <v>2026-08-08T07:06:25.102Z</v>
       </c>
       <c r="F16" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="17">
@@ -969,13 +969,13 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>0.81 sec</v>
+        <v>4.02 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-03T18:44:20.289Z</v>
+        <v>2026-08-08T07:06:29.122Z</v>
       </c>
       <c r="F17" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="18">
@@ -989,13 +989,13 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.87 sec</v>
+        <v>3.85 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-03T18:44:21.163Z</v>
+        <v>2026-08-08T07:06:32.973Z</v>
       </c>
       <c r="F18" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="19">
@@ -1009,13 +1009,13 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.95 sec</v>
+        <v>4.06 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-03T18:44:22.113Z</v>
+        <v>2026-08-08T07:06:37.037Z</v>
       </c>
       <c r="F19" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="20">
@@ -1029,13 +1029,13 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.72 sec</v>
+        <v>4.02 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-03T18:44:22.835Z</v>
+        <v>2026-08-08T07:06:41.059Z</v>
       </c>
       <c r="F20" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="21">
@@ -1049,13 +1049,13 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>1.02 sec</v>
+        <v>4.01 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-03T18:44:23.860Z</v>
+        <v>2026-08-08T07:06:45.074Z</v>
       </c>
       <c r="F21" t="str">
-        <v>Email address does not exist.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="22">
@@ -1069,13 +1069,13 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.93 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-03T18:44:24.790Z</v>
+        <v>2026-08-08T07:06:46.117Z</v>
       </c>
       <c r="F22" t="str">
-        <v>Email address does not exist.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="23">
@@ -1089,10 +1089,10 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.67 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-03T18:44:25.455Z</v>
+        <v>2026-08-08T07:06:46.859Z</v>
       </c>
       <c r="F23" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1109,10 +1109,10 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>0.72 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-03T18:44:26.171Z</v>
+        <v>2026-08-08T07:06:47.637Z</v>
       </c>
       <c r="F24" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1129,10 +1129,10 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.98 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-03T18:44:27.153Z</v>
+        <v>2026-08-08T07:06:48.559Z</v>
       </c>
       <c r="F25" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1149,10 +1149,10 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.78 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-03T18:44:27.928Z</v>
+        <v>2026-08-08T07:06:49.385Z</v>
       </c>
       <c r="F26" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1169,10 +1169,10 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>1.09 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-03T18:44:29.014Z</v>
+        <v>2026-08-08T07:06:50.405Z</v>
       </c>
       <c r="F27" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1189,10 +1189,10 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>0.85 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-03T18:44:29.861Z</v>
+        <v>2026-08-08T07:06:51.353Z</v>
       </c>
       <c r="F28" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1209,10 +1209,10 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.66 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-03T18:44:30.521Z</v>
+        <v>2026-08-08T07:06:52.210Z</v>
       </c>
       <c r="F29" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1229,10 +1229,10 @@
         <v>PASS</v>
       </c>
       <c r="D30" t="str">
-        <v>0.96 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-03T18:44:31.480Z</v>
+        <v>2026-08-08T07:06:53.046Z</v>
       </c>
       <c r="F30" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1249,10 +1249,10 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.96 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-03T18:44:32.440Z</v>
+        <v>2026-08-08T07:06:54.355Z</v>
       </c>
       <c r="F31" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1272,7 +1272,7 @@
         <v>0.88 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-03T18:44:33.317Z</v>
+        <v>2026-08-08T07:06:55.230Z</v>
       </c>
       <c r="F32" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1289,10 +1289,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.79 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-03T18:44:34.106Z</v>
+        <v>2026-08-08T07:06:56.312Z</v>
       </c>
       <c r="F33" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1309,10 +1309,10 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.89 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-03T18:44:34.995Z</v>
+        <v>2026-08-08T07:06:57.236Z</v>
       </c>
       <c r="F34" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1329,10 +1329,10 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.59 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-03T18:44:35.584Z</v>
+        <v>2026-08-08T07:06:58.034Z</v>
       </c>
       <c r="F35" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1349,10 +1349,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.70 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-03T18:44:36.282Z</v>
+        <v>2026-08-08T07:06:58.799Z</v>
       </c>
       <c r="F36" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1369,10 +1369,10 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>0.79 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-03T18:44:37.069Z</v>
+        <v>2026-08-08T07:06:59.816Z</v>
       </c>
       <c r="F37" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1389,10 +1389,10 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>0.66 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-03T18:44:37.731Z</v>
+        <v>2026-08-08T07:07:00.978Z</v>
       </c>
       <c r="F38" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1409,10 +1409,10 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.97 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-03T18:44:38.706Z</v>
+        <v>2026-08-08T07:07:01.974Z</v>
       </c>
       <c r="F39" t="str">
         <v>Too many authentication attempts. Please try again after 15 minutes.</v>
@@ -1429,13 +1429,13 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.92 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-03T18:44:39.623Z</v>
+        <v>2026-08-08T07:07:02.798Z</v>
       </c>
       <c r="F40" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="41">
@@ -1449,13 +1449,13 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.85 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-03T18:44:40.477Z</v>
+        <v>2026-08-08T07:07:03.811Z</v>
       </c>
       <c r="F41" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="42">
@@ -1469,13 +1469,13 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.93 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-03T18:44:41.405Z</v>
+        <v>2026-08-08T07:07:04.607Z</v>
       </c>
       <c r="F42" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="43">
@@ -1489,10 +1489,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.98 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-03T18:44:42.387Z</v>
+        <v>2026-08-08T07:07:05.532Z</v>
       </c>
       <c r="F43" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1509,10 +1509,10 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.90 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-03T18:44:43.288Z</v>
+        <v>2026-08-08T07:07:06.458Z</v>
       </c>
       <c r="F44" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1529,10 +1529,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.97 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-03T18:44:44.256Z</v>
+        <v>2026-08-08T07:07:07.385Z</v>
       </c>
       <c r="F45" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1549,10 +1549,10 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.66 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-03T18:44:44.915Z</v>
+        <v>2026-08-08T07:07:08.214Z</v>
       </c>
       <c r="F46" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1569,10 +1569,10 @@
         <v>PASS</v>
       </c>
       <c r="D47" t="str">
-        <v>0.85 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-03T18:44:45.768Z</v>
+        <v>2026-08-08T07:07:09.089Z</v>
       </c>
       <c r="F47" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1589,10 +1589,10 @@
         <v>PASS</v>
       </c>
       <c r="D48" t="str">
-        <v>0.92 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-03T18:44:46.691Z</v>
+        <v>2026-08-08T07:07:09.926Z</v>
       </c>
       <c r="F48" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1609,10 +1609,10 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>1.03 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-03T18:44:47.722Z</v>
+        <v>2026-08-08T07:07:10.898Z</v>
       </c>
       <c r="F49" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1629,10 +1629,10 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>0.62 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-03T18:44:48.345Z</v>
+        <v>2026-08-08T07:07:11.967Z</v>
       </c>
       <c r="F50" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1649,10 +1649,10 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.76 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-03T18:44:49.104Z</v>
+        <v>2026-08-08T07:07:12.966Z</v>
       </c>
       <c r="F51" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1669,10 +1669,10 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.88 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-03T18:44:49.986Z</v>
+        <v>2026-08-08T07:07:13.864Z</v>
       </c>
       <c r="F52" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1689,10 +1689,10 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>0.84 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-03T18:44:50.824Z</v>
+        <v>2026-08-08T07:07:14.859Z</v>
       </c>
       <c r="F53" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1709,10 +1709,10 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.91 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-03T18:44:51.735Z</v>
+        <v>2026-08-08T07:07:15.678Z</v>
       </c>
       <c r="F54" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1729,10 +1729,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>1.06 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-03T18:44:52.800Z</v>
+        <v>2026-08-08T07:07:16.634Z</v>
       </c>
       <c r="F55" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1749,10 +1749,10 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.95 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-03T18:44:53.750Z</v>
+        <v>2026-08-08T07:07:17.470Z</v>
       </c>
       <c r="F56" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1769,10 +1769,10 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.81 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-03T18:44:54.555Z</v>
+        <v>2026-08-08T07:07:18.419Z</v>
       </c>
       <c r="F57" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1789,10 +1789,10 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.73 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-03T18:44:55.283Z</v>
+        <v>2026-08-08T07:07:19.404Z</v>
       </c>
       <c r="F58" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1809,10 +1809,10 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.74 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-03T18:44:56.027Z</v>
+        <v>2026-08-08T07:07:20.193Z</v>
       </c>
       <c r="F59" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1829,10 +1829,10 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>0.68 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-03T18:44:56.708Z</v>
+        <v>2026-08-08T07:07:21.011Z</v>
       </c>
       <c r="F60" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1849,10 +1849,10 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.77 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-03T18:44:57.482Z</v>
+        <v>2026-08-08T07:07:22.026Z</v>
       </c>
       <c r="F61" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1869,10 +1869,10 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.66 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-03T18:44:58.138Z</v>
+        <v>2026-08-08T07:07:23.072Z</v>
       </c>
       <c r="F62" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1889,10 +1889,10 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>1.25 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-03T18:44:59.391Z</v>
+        <v>2026-08-08T07:07:24.037Z</v>
       </c>
       <c r="F63" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1909,10 +1909,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.93 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-03T18:45:00.317Z</v>
+        <v>2026-08-08T07:07:25.137Z</v>
       </c>
       <c r="F64" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1929,10 +1929,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.92 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-03T18:45:01.240Z</v>
+        <v>2026-08-08T07:07:25.926Z</v>
       </c>
       <c r="F65" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1949,10 +1949,10 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.61 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-03T18:45:01.850Z</v>
+        <v>2026-08-08T07:07:26.772Z</v>
       </c>
       <c r="F66" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1969,10 +1969,10 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>1.08 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-03T18:45:02.935Z</v>
+        <v>2026-08-08T07:07:27.748Z</v>
       </c>
       <c r="F67" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -1989,10 +1989,10 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.63 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-03T18:45:03.565Z</v>
+        <v>2026-08-08T07:07:28.622Z</v>
       </c>
       <c r="F68" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2009,10 +2009,10 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.99 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-03T18:45:04.551Z</v>
+        <v>2026-08-08T07:07:29.708Z</v>
       </c>
       <c r="F69" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2029,10 +2029,10 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.66 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-03T18:45:05.207Z</v>
+        <v>2026-08-08T07:07:30.543Z</v>
       </c>
       <c r="F70" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2049,10 +2049,10 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.88 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-03T18:45:06.089Z</v>
+        <v>2026-08-08T07:07:31.394Z</v>
       </c>
       <c r="F71" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2069,10 +2069,10 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.90 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-03T18:45:06.993Z</v>
+        <v>2026-08-08T07:07:32.141Z</v>
       </c>
       <c r="F72" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2089,10 +2089,10 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>0.91 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-03T18:45:07.904Z</v>
+        <v>2026-08-08T07:07:33.176Z</v>
       </c>
       <c r="F73" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2109,10 +2109,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>1.06 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-03T18:45:08.960Z</v>
+        <v>2026-08-08T07:07:33.993Z</v>
       </c>
       <c r="F74" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2129,10 +2129,10 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>0.92 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-03T18:45:09.881Z</v>
+        <v>2026-08-08T07:07:35.101Z</v>
       </c>
       <c r="F75" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2149,10 +2149,10 @@
         <v>PASS</v>
       </c>
       <c r="D76" t="str">
-        <v>1.01 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-03T18:45:10.891Z</v>
+        <v>2026-08-08T07:07:36.089Z</v>
       </c>
       <c r="F76" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2169,10 +2169,10 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.61 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-03T18:45:11.504Z</v>
+        <v>2026-08-08T07:07:36.863Z</v>
       </c>
       <c r="F77" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2189,10 +2189,10 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.67 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-03T18:45:12.170Z</v>
+        <v>2026-08-08T07:07:37.692Z</v>
       </c>
       <c r="F78" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2209,10 +2209,10 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>1.05 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-03T18:45:13.223Z</v>
+        <v>2026-08-08T07:07:38.710Z</v>
       </c>
       <c r="F79" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2229,10 +2229,10 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.92 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-03T18:45:14.141Z</v>
+        <v>2026-08-08T07:07:39.614Z</v>
       </c>
       <c r="F80" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2249,10 +2249,10 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>1.11 sec</v>
+        <v>1.20 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-03T18:45:15.256Z</v>
+        <v>2026-08-08T07:07:40.814Z</v>
       </c>
       <c r="F81" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2269,10 +2269,10 @@
         <v>PASS</v>
       </c>
       <c r="D82" t="str">
-        <v>1.12 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-03T18:45:16.372Z</v>
+        <v>2026-08-08T07:07:41.791Z</v>
       </c>
       <c r="F82" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2289,10 +2289,10 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.92 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-03T18:45:17.288Z</v>
+        <v>2026-08-08T07:07:42.592Z</v>
       </c>
       <c r="F83" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2309,10 +2309,10 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>0.83 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-03T18:45:18.118Z</v>
+        <v>2026-08-08T07:07:43.345Z</v>
       </c>
       <c r="F84" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2329,10 +2329,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>1.14 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-03T18:45:19.256Z</v>
+        <v>2026-08-08T07:07:44.321Z</v>
       </c>
       <c r="F85" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2349,10 +2349,10 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.92 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-03T18:45:20.179Z</v>
+        <v>2026-08-08T07:07:45.404Z</v>
       </c>
       <c r="F86" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2369,10 +2369,10 @@
         <v>PASS</v>
       </c>
       <c r="D87" t="str">
-        <v>0.89 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-03T18:45:21.068Z</v>
+        <v>2026-08-08T07:07:46.571Z</v>
       </c>
       <c r="F87" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2389,10 +2389,10 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>0.95 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-03T18:45:22.019Z</v>
+        <v>2026-08-08T07:07:47.616Z</v>
       </c>
       <c r="F88" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2409,10 +2409,10 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.89 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-03T18:45:22.911Z</v>
+        <v>2026-08-08T07:07:48.562Z</v>
       </c>
       <c r="F89" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2429,10 +2429,10 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.85 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-03T18:45:23.762Z</v>
+        <v>2026-08-08T07:07:49.387Z</v>
       </c>
       <c r="F90" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2449,10 +2449,10 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>1.06 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-03T18:45:24.825Z</v>
+        <v>2026-08-08T07:07:50.310Z</v>
       </c>
       <c r="F91" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2469,10 +2469,10 @@
         <v>PASS</v>
       </c>
       <c r="D92" t="str">
-        <v>0.66 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-03T18:45:25.483Z</v>
+        <v>2026-08-08T07:07:51.381Z</v>
       </c>
       <c r="F92" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2489,10 +2489,10 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>1.09 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-03T18:45:26.578Z</v>
+        <v>2026-08-08T07:07:52.208Z</v>
       </c>
       <c r="F93" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2509,10 +2509,10 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.66 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-03T18:45:27.234Z</v>
+        <v>2026-08-08T07:07:53.158Z</v>
       </c>
       <c r="F94" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2529,10 +2529,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.86 sec</v>
+        <v>0.64 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-03T18:45:28.092Z</v>
+        <v>2026-08-08T07:07:53.802Z</v>
       </c>
       <c r="F95" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2549,10 +2549,10 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.63 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-03T18:45:28.725Z</v>
+        <v>2026-08-08T07:07:54.597Z</v>
       </c>
       <c r="F96" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2569,10 +2569,10 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>1.15 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-03T18:45:29.879Z</v>
+        <v>2026-08-08T07:07:55.347Z</v>
       </c>
       <c r="F97" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2589,10 +2589,10 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.94 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-03T18:45:30.817Z</v>
+        <v>2026-08-08T07:07:56.200Z</v>
       </c>
       <c r="F98" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2609,10 +2609,10 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>1.10 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-03T18:45:31.918Z</v>
+        <v>2026-08-08T07:07:57.168Z</v>
       </c>
       <c r="F99" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2629,10 +2629,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>1.02 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-03T18:45:32.936Z</v>
+        <v>2026-08-08T07:07:58.059Z</v>
       </c>
       <c r="F100" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2649,10 +2649,10 @@
         <v>PASS</v>
       </c>
       <c r="D101" t="str">
-        <v>0.95 sec</v>
+        <v>0.55 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-03T18:45:33.889Z</v>
+        <v>2026-08-08T07:07:58.613Z</v>
       </c>
       <c r="F101" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>1.03 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-03T18:45:34.923Z</v>
+        <v>2026-08-08T07:07:59.394Z</v>
       </c>
       <c r="F102" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2689,10 +2689,10 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>1.10 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-03T18:45:36.023Z</v>
+        <v>2026-08-08T07:08:00.135Z</v>
       </c>
       <c r="F103" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2709,10 +2709,10 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>1.26 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-03T18:45:37.281Z</v>
+        <v>2026-08-08T07:08:00.794Z</v>
       </c>
       <c r="F104" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2729,10 +2729,10 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>1.32 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-03T18:45:38.606Z</v>
+        <v>2026-08-08T07:08:01.577Z</v>
       </c>
       <c r="F105" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2749,10 +2749,10 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.92 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-03T18:45:39.524Z</v>
+        <v>2026-08-08T07:08:02.156Z</v>
       </c>
       <c r="F106" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2769,10 +2769,10 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.88 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-03T18:45:40.407Z</v>
+        <v>2026-08-08T07:08:02.949Z</v>
       </c>
       <c r="F107" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2789,10 +2789,10 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.94 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-03T18:45:41.343Z</v>
+        <v>2026-08-08T07:08:03.631Z</v>
       </c>
       <c r="F108" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2809,10 +2809,10 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>1.12 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-03T18:45:42.464Z</v>
+        <v>2026-08-08T07:08:04.705Z</v>
       </c>
       <c r="F109" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2829,10 +2829,10 @@
         <v>PASS</v>
       </c>
       <c r="D110" t="str">
-        <v>0.85 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-03T18:45:43.312Z</v>
+        <v>2026-08-08T07:08:05.728Z</v>
       </c>
       <c r="F110" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2849,10 +2849,10 @@
         <v>PASS</v>
       </c>
       <c r="D111" t="str">
-        <v>1.19 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-03T18:45:44.506Z</v>
+        <v>2026-08-08T07:08:06.686Z</v>
       </c>
       <c r="F111" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2869,10 +2869,10 @@
         <v>PASS</v>
       </c>
       <c r="D112" t="str">
-        <v>1.12 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-03T18:45:45.629Z</v>
+        <v>2026-08-08T07:08:07.563Z</v>
       </c>
       <c r="F112" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2889,10 +2889,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>1.04 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-03T18:45:46.670Z</v>
+        <v>2026-08-08T07:08:08.380Z</v>
       </c>
       <c r="F113" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2909,10 +2909,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.97 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-03T18:45:47.636Z</v>
+        <v>2026-08-08T07:08:09.271Z</v>
       </c>
       <c r="F114" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2929,10 +2929,10 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>0.91 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-03T18:45:48.547Z</v>
+        <v>2026-08-08T07:08:10.449Z</v>
       </c>
       <c r="F115" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2949,10 +2949,10 @@
         <v>PASS</v>
       </c>
       <c r="D116" t="str">
-        <v>0.79 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-03T18:45:49.338Z</v>
+        <v>2026-08-08T07:08:11.190Z</v>
       </c>
       <c r="F116" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2969,10 +2969,10 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.90 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-03T18:45:50.237Z</v>
+        <v>2026-08-08T07:08:12.128Z</v>
       </c>
       <c r="F117" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -2989,10 +2989,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.82 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-03T18:45:51.053Z</v>
+        <v>2026-08-08T07:08:12.958Z</v>
       </c>
       <c r="F118" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3009,10 +3009,10 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.81 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-03T18:45:51.863Z</v>
+        <v>2026-08-08T07:08:13.762Z</v>
       </c>
       <c r="F119" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3029,10 +3029,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.70 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-03T18:45:52.559Z</v>
+        <v>2026-08-08T07:08:14.642Z</v>
       </c>
       <c r="F120" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3049,10 +3049,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.89 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-03T18:45:53.451Z</v>
+        <v>2026-08-08T07:08:15.853Z</v>
       </c>
       <c r="F121" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3069,10 +3069,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.56 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-03T18:45:54.009Z</v>
+        <v>2026-08-08T07:08:16.826Z</v>
       </c>
       <c r="F122" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3089,10 +3089,10 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.84 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-03T18:45:54.847Z</v>
+        <v>2026-08-08T07:08:17.759Z</v>
       </c>
       <c r="F123" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3109,10 +3109,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.77 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-03T18:45:55.617Z</v>
+        <v>2026-08-08T07:08:18.818Z</v>
       </c>
       <c r="F124" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3129,10 +3129,10 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>0.97 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-03T18:45:56.585Z</v>
+        <v>2026-08-08T07:08:19.839Z</v>
       </c>
       <c r="F125" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3149,10 +3149,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.73 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-03T18:45:57.317Z</v>
+        <v>2026-08-08T07:08:20.535Z</v>
       </c>
       <c r="F126" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3169,10 +3169,10 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>0.65 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-03T18:45:57.965Z</v>
+        <v>2026-08-08T07:08:21.487Z</v>
       </c>
       <c r="F127" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3189,10 +3189,10 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.55 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-03T18:45:58.518Z</v>
+        <v>2026-08-08T07:08:22.446Z</v>
       </c>
       <c r="F128" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3209,10 +3209,10 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.63 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-03T18:45:59.152Z</v>
+        <v>2026-08-08T07:08:23.376Z</v>
       </c>
       <c r="F129" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3229,10 +3229,10 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.59 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-03T18:45:59.742Z</v>
+        <v>2026-08-08T07:08:24.204Z</v>
       </c>
       <c r="F130" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3249,10 +3249,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.79 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-03T18:46:00.532Z</v>
+        <v>2026-08-08T07:08:25.152Z</v>
       </c>
       <c r="F131" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3269,10 +3269,10 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.74 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-03T18:46:01.272Z</v>
+        <v>2026-08-08T07:08:26.104Z</v>
       </c>
       <c r="F132" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3289,10 +3289,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.83 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-03T18:46:02.099Z</v>
+        <v>2026-08-08T07:08:27.152Z</v>
       </c>
       <c r="F133" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3309,10 +3309,10 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.59 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-03T18:46:02.685Z</v>
+        <v>2026-08-08T07:08:28.022Z</v>
       </c>
       <c r="F134" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3329,10 +3329,10 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.69 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-03T18:46:03.381Z</v>
+        <v>2026-08-08T07:08:29.149Z</v>
       </c>
       <c r="F135" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3349,10 +3349,10 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.79 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-03T18:46:04.167Z</v>
+        <v>2026-08-08T07:08:29.989Z</v>
       </c>
       <c r="F136" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3369,10 +3369,10 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.75 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-03T18:46:04.917Z</v>
+        <v>2026-08-08T07:08:30.794Z</v>
       </c>
       <c r="F137" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3389,10 +3389,10 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.49 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-03T18:46:05.408Z</v>
+        <v>2026-08-08T07:08:31.656Z</v>
       </c>
       <c r="F138" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3409,10 +3409,10 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.88 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-03T18:46:06.286Z</v>
+        <v>2026-08-08T07:08:32.937Z</v>
       </c>
       <c r="F139" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3429,10 +3429,10 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.55 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-03T18:46:06.838Z</v>
+        <v>2026-08-08T07:08:33.969Z</v>
       </c>
       <c r="F140" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3449,10 +3449,10 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.93 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-03T18:46:07.772Z</v>
+        <v>2026-08-08T07:08:35.091Z</v>
       </c>
       <c r="F141" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3469,10 +3469,10 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.83 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-03T18:46:08.605Z</v>
+        <v>2026-08-08T07:08:36.108Z</v>
       </c>
       <c r="F142" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3489,10 +3489,10 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.57 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-03T18:46:09.173Z</v>
+        <v>2026-08-08T07:08:37.104Z</v>
       </c>
       <c r="F143" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3509,10 +3509,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.95 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-03T18:46:10.120Z</v>
+        <v>2026-08-08T07:08:38.164Z</v>
       </c>
       <c r="F144" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3529,10 +3529,10 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.66 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-03T18:46:10.779Z</v>
+        <v>2026-08-08T07:08:39.188Z</v>
       </c>
       <c r="F145" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3549,10 +3549,10 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>0.52 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-03T18:46:11.298Z</v>
+        <v>2026-08-08T07:08:40.130Z</v>
       </c>
       <c r="F146" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3569,10 +3569,10 @@
         <v>PASS</v>
       </c>
       <c r="D147" t="str">
-        <v>0.65 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-03T18:46:11.948Z</v>
+        <v>2026-08-08T07:08:41.112Z</v>
       </c>
       <c r="F147" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3592,7 +3592,7 @@
         <v>0.85 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-03T18:46:12.803Z</v>
+        <v>2026-08-08T07:08:41.965Z</v>
       </c>
       <c r="F148" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3609,10 +3609,10 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>0.72 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-03T18:46:13.519Z</v>
+        <v>2026-08-08T07:08:42.791Z</v>
       </c>
       <c r="F149" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3629,10 +3629,10 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>0.54 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-03T18:46:14.059Z</v>
+        <v>2026-08-08T07:08:43.834Z</v>
       </c>
       <c r="F150" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3649,10 +3649,10 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.88 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-03T18:46:14.937Z</v>
+        <v>2026-08-08T07:08:45.114Z</v>
       </c>
       <c r="F151" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3669,10 +3669,10 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.87 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-03T18:46:15.805Z</v>
+        <v>2026-08-08T07:08:46.050Z</v>
       </c>
       <c r="F152" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3689,10 +3689,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.71 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-03T18:46:16.516Z</v>
+        <v>2026-08-08T07:08:47.181Z</v>
       </c>
       <c r="F153" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3709,10 +3709,10 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>0.78 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-03T18:46:17.295Z</v>
+        <v>2026-08-08T07:08:48.197Z</v>
       </c>
       <c r="F154" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3729,10 +3729,10 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.74 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-03T18:46:18.035Z</v>
+        <v>2026-08-08T07:08:49.058Z</v>
       </c>
       <c r="F155" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3749,10 +3749,10 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>0.50 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-03T18:46:18.538Z</v>
+        <v>2026-08-08T07:08:50.092Z</v>
       </c>
       <c r="F156" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3769,10 +3769,10 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>0.91 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-03T18:46:19.448Z</v>
+        <v>2026-08-08T07:08:51.190Z</v>
       </c>
       <c r="F157" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3789,10 +3789,10 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.79 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-03T18:46:20.235Z</v>
+        <v>2026-08-08T07:08:51.993Z</v>
       </c>
       <c r="F158" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3809,10 +3809,10 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>0.93 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-03T18:46:21.166Z</v>
+        <v>2026-08-08T07:08:52.967Z</v>
       </c>
       <c r="F159" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3829,10 +3829,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.70 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-03T18:46:21.866Z</v>
+        <v>2026-08-08T07:08:54.099Z</v>
       </c>
       <c r="F160" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3849,10 +3849,10 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.78 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-03T18:46:22.644Z</v>
+        <v>2026-08-08T07:08:55.055Z</v>
       </c>
       <c r="F161" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3869,10 +3869,10 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.51 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-03T18:46:23.151Z</v>
+        <v>2026-08-08T07:08:56.174Z</v>
       </c>
       <c r="F162" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3889,10 +3889,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.60 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-03T18:46:23.750Z</v>
+        <v>2026-08-08T07:08:56.980Z</v>
       </c>
       <c r="F163" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3909,10 +3909,10 @@
         <v>PASS</v>
       </c>
       <c r="D164" t="str">
-        <v>0.87 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-03T18:46:24.619Z</v>
+        <v>2026-08-08T07:08:57.995Z</v>
       </c>
       <c r="F164" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3929,10 +3929,10 @@
         <v>PASS</v>
       </c>
       <c r="D165" t="str">
-        <v>0.88 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-03T18:46:25.502Z</v>
+        <v>2026-08-08T07:08:58.934Z</v>
       </c>
       <c r="F165" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3949,10 +3949,10 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.83 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-03T18:46:26.331Z</v>
+        <v>2026-08-08T07:08:59.908Z</v>
       </c>
       <c r="F166" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3969,10 +3969,10 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.82 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-03T18:46:27.154Z</v>
+        <v>2026-08-08T07:09:01.006Z</v>
       </c>
       <c r="F167" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -3989,10 +3989,10 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.67 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-03T18:46:27.821Z</v>
+        <v>2026-08-08T07:09:01.883Z</v>
       </c>
       <c r="F168" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4009,10 +4009,10 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.68 sec</v>
+        <v>1.29 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-03T18:46:28.502Z</v>
+        <v>2026-08-08T07:09:03.174Z</v>
       </c>
       <c r="F169" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4029,10 +4029,10 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.58 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-03T18:46:29.082Z</v>
+        <v>2026-08-08T07:09:04.057Z</v>
       </c>
       <c r="F170" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4049,10 +4049,10 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.88 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-03T18:46:29.966Z</v>
+        <v>2026-08-08T07:09:05.000Z</v>
       </c>
       <c r="F171" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4069,10 +4069,10 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>0.80 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-03T18:46:30.764Z</v>
+        <v>2026-08-08T07:09:05.994Z</v>
       </c>
       <c r="F172" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4089,10 +4089,10 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>0.78 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-03T18:46:31.546Z</v>
+        <v>2026-08-08T07:09:06.853Z</v>
       </c>
       <c r="F173" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4109,10 +4109,10 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.97 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-03T18:46:32.518Z</v>
+        <v>2026-08-08T07:09:07.584Z</v>
       </c>
       <c r="F174" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4129,10 +4129,10 @@
         <v>PASS</v>
       </c>
       <c r="D175" t="str">
-        <v>1.08 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-03T18:46:33.603Z</v>
+        <v>2026-08-08T07:09:08.575Z</v>
       </c>
       <c r="F175" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4149,10 +4149,10 @@
         <v>PASS</v>
       </c>
       <c r="D176" t="str">
-        <v>0.83 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-03T18:46:34.434Z</v>
+        <v>2026-08-08T07:09:09.841Z</v>
       </c>
       <c r="F176" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4169,10 +4169,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.90 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-03T18:46:35.335Z</v>
+        <v>2026-08-08T07:09:10.755Z</v>
       </c>
       <c r="F177" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4189,10 +4189,10 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.98 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-03T18:46:36.317Z</v>
+        <v>2026-08-08T07:09:11.491Z</v>
       </c>
       <c r="F178" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4209,10 +4209,10 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.98 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-03T18:46:37.300Z</v>
+        <v>2026-08-08T07:09:12.446Z</v>
       </c>
       <c r="F179" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4229,10 +4229,10 @@
         <v>PASS</v>
       </c>
       <c r="D180" t="str">
-        <v>0.96 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-03T18:46:38.262Z</v>
+        <v>2026-08-08T07:09:13.756Z</v>
       </c>
       <c r="F180" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4249,10 +4249,10 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>0.89 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-03T18:46:39.150Z</v>
+        <v>2026-08-08T07:09:15.306Z</v>
       </c>
       <c r="F181" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4269,10 +4269,10 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>0.81 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-03T18:46:39.965Z</v>
+        <v>2026-08-08T07:09:16.494Z</v>
       </c>
       <c r="F182" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4289,10 +4289,10 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>1.04 sec</v>
+        <v>2.20 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-03T18:46:41.003Z</v>
+        <v>2026-08-08T07:09:18.692Z</v>
       </c>
       <c r="F183" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4309,10 +4309,10 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>0.95 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-03T18:46:41.956Z</v>
+        <v>2026-08-08T07:09:20.037Z</v>
       </c>
       <c r="F184" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4329,10 +4329,10 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.91 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-03T18:46:42.870Z</v>
+        <v>2026-08-08T07:09:21.346Z</v>
       </c>
       <c r="F185" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4349,10 +4349,10 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.93 sec</v>
+        <v>2.18 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-03T18:46:43.797Z</v>
+        <v>2026-08-08T07:09:23.527Z</v>
       </c>
       <c r="F186" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4369,10 +4369,10 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>1.14 sec</v>
+        <v>1.66 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-03T18:46:44.936Z</v>
+        <v>2026-08-08T07:09:25.183Z</v>
       </c>
       <c r="F187" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4389,10 +4389,10 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>0.96 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-03T18:46:45.896Z</v>
+        <v>2026-08-08T07:09:26.344Z</v>
       </c>
       <c r="F188" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4409,10 +4409,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.86 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-03T18:46:46.760Z</v>
+        <v>2026-08-08T07:09:27.516Z</v>
       </c>
       <c r="F189" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4429,10 +4429,10 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>0.69 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-03T18:46:47.445Z</v>
+        <v>2026-08-08T07:09:28.523Z</v>
       </c>
       <c r="F190" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4449,10 +4449,10 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.65 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-03T18:46:48.094Z</v>
+        <v>2026-08-08T07:09:29.807Z</v>
       </c>
       <c r="F191" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4469,10 +4469,10 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.69 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-03T18:46:48.787Z</v>
+        <v>2026-08-08T07:09:30.735Z</v>
       </c>
       <c r="F192" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4489,10 +4489,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.88 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-03T18:46:49.663Z</v>
+        <v>2026-08-08T07:09:31.508Z</v>
       </c>
       <c r="F193" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4509,10 +4509,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.71 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-03T18:46:50.371Z</v>
+        <v>2026-08-08T07:09:32.312Z</v>
       </c>
       <c r="F194" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4529,10 +4529,10 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.98 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-03T18:46:51.351Z</v>
+        <v>2026-08-08T07:09:33.157Z</v>
       </c>
       <c r="F195" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4549,10 +4549,10 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.96 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-03T18:46:52.313Z</v>
+        <v>2026-08-08T07:09:33.873Z</v>
       </c>
       <c r="F196" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4569,10 +4569,10 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>1.01 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-03T18:46:53.326Z</v>
+        <v>2026-08-08T07:09:34.559Z</v>
       </c>
       <c r="F197" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4589,10 +4589,10 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>1.19 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-03T18:46:54.511Z</v>
+        <v>2026-08-08T07:09:35.256Z</v>
       </c>
       <c r="F198" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4609,10 +4609,10 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>1.48 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-03T18:46:55.990Z</v>
+        <v>2026-08-08T07:09:36.093Z</v>
       </c>
       <c r="F199" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4629,10 +4629,10 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.94 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-03T18:46:56.927Z</v>
+        <v>2026-08-08T07:09:36.867Z</v>
       </c>
       <c r="F200" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4649,10 +4649,10 @@
         <v>PASS</v>
       </c>
       <c r="D201" t="str">
-        <v>1.15 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-03T18:46:58.081Z</v>
+        <v>2026-08-08T07:09:37.904Z</v>
       </c>
       <c r="F201" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4672,7 +4672,7 @@
         <v>1.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-03T18:46:59.089Z</v>
+        <v>2026-08-08T07:09:38.914Z</v>
       </c>
       <c r="F202" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4689,10 +4689,10 @@
         <v>PASS</v>
       </c>
       <c r="D203" t="str">
-        <v>0.87 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-03T18:46:59.962Z</v>
+        <v>2026-08-08T07:09:39.735Z</v>
       </c>
       <c r="F203" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4709,10 +4709,10 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>1.08 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-03T18:47:01.043Z</v>
+        <v>2026-08-08T07:09:40.505Z</v>
       </c>
       <c r="F204" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4732,7 +4732,7 @@
         <v>0.97 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-03T18:47:02.017Z</v>
+        <v>2026-08-08T07:09:41.472Z</v>
       </c>
       <c r="F205" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4749,10 +4749,10 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.95 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-03T18:47:02.964Z</v>
+        <v>2026-08-08T07:09:42.667Z</v>
       </c>
       <c r="F206" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4769,10 +4769,10 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>1.16 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-03T18:47:04.127Z</v>
+        <v>2026-08-08T07:09:43.682Z</v>
       </c>
       <c r="F207" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4789,10 +4789,10 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>1.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-03T18:47:05.127Z</v>
+        <v>2026-08-08T07:09:44.407Z</v>
       </c>
       <c r="F208" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4809,10 +4809,10 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.91 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-03T18:47:06.032Z</v>
+        <v>2026-08-08T07:09:45.154Z</v>
       </c>
       <c r="F209" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4829,10 +4829,10 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.62 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-03T18:47:06.656Z</v>
+        <v>2026-08-08T07:09:46.227Z</v>
       </c>
       <c r="F210" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4849,10 +4849,10 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>0.86 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-03T18:47:07.520Z</v>
+        <v>2026-08-08T07:09:47.415Z</v>
       </c>
       <c r="F211" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4869,10 +4869,10 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.78 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-03T18:47:08.302Z</v>
+        <v>2026-08-08T07:09:48.391Z</v>
       </c>
       <c r="F212" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4889,10 +4889,10 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.81 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-03T18:47:09.110Z</v>
+        <v>2026-08-08T07:09:49.432Z</v>
       </c>
       <c r="F213" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4909,10 +4909,10 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>0.93 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-03T18:47:10.036Z</v>
+        <v>2026-08-08T07:09:50.579Z</v>
       </c>
       <c r="F214" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4929,10 +4929,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.81 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-03T18:47:10.847Z</v>
+        <v>2026-08-08T07:09:51.675Z</v>
       </c>
       <c r="F215" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4949,10 +4949,10 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>0.81 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-03T18:47:11.655Z</v>
+        <v>2026-08-08T07:09:52.362Z</v>
       </c>
       <c r="F216" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4969,10 +4969,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.67 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-03T18:47:12.329Z</v>
+        <v>2026-08-08T07:09:53.138Z</v>
       </c>
       <c r="F217" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -4989,10 +4989,10 @@
         <v>PASS</v>
       </c>
       <c r="D218" t="str">
-        <v>0.57 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-03T18:47:12.899Z</v>
+        <v>2026-08-08T07:09:53.845Z</v>
       </c>
       <c r="F218" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5009,10 +5009,10 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.91 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-03T18:47:13.806Z</v>
+        <v>2026-08-08T07:09:55.051Z</v>
       </c>
       <c r="F219" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5029,10 +5029,10 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.79 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-03T18:47:14.591Z</v>
+        <v>2026-08-08T07:09:56.123Z</v>
       </c>
       <c r="F220" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5049,10 +5049,10 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.81 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-03T18:47:15.401Z</v>
+        <v>2026-08-08T07:09:57.018Z</v>
       </c>
       <c r="F221" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5069,10 +5069,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.74 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-03T18:47:16.145Z</v>
+        <v>2026-08-08T07:09:57.985Z</v>
       </c>
       <c r="F222" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5089,10 +5089,10 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>0.89 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-03T18:47:17.033Z</v>
+        <v>2026-08-08T07:09:58.996Z</v>
       </c>
       <c r="F223" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5109,10 +5109,10 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>0.81 sec</v>
+        <v>1.30 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-03T18:47:17.848Z</v>
+        <v>2026-08-08T07:10:00.296Z</v>
       </c>
       <c r="F224" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5129,10 +5129,10 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.92 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-03T18:47:18.767Z</v>
+        <v>2026-08-08T07:10:01.360Z</v>
       </c>
       <c r="F225" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5152,7 +5152,7 @@
         <v>0.87 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-03T18:47:19.636Z</v>
+        <v>2026-08-08T07:10:02.233Z</v>
       </c>
       <c r="F226" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5169,10 +5169,10 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.76 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-03T18:47:20.393Z</v>
+        <v>2026-08-08T07:10:03.139Z</v>
       </c>
       <c r="F227" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5189,10 +5189,10 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.53 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-03T18:47:20.927Z</v>
+        <v>2026-08-08T07:10:03.810Z</v>
       </c>
       <c r="F228" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5209,10 +5209,10 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.60 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-03T18:47:21.525Z</v>
+        <v>2026-08-08T07:10:04.990Z</v>
       </c>
       <c r="F229" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5229,10 +5229,10 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>0.57 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-03T18:47:22.099Z</v>
+        <v>2026-08-08T07:10:06.262Z</v>
       </c>
       <c r="F230" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5249,10 +5249,10 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>0.92 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-03T18:47:23.020Z</v>
+        <v>2026-08-08T07:10:07.424Z</v>
       </c>
       <c r="F231" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5269,10 +5269,10 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>0.79 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-03T18:47:23.813Z</v>
+        <v>2026-08-08T07:10:08.447Z</v>
       </c>
       <c r="F232" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5289,10 +5289,10 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.57 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-03T18:47:24.381Z</v>
+        <v>2026-08-08T07:10:09.228Z</v>
       </c>
       <c r="F233" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5309,10 +5309,10 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.55 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-03T18:47:24.928Z</v>
+        <v>2026-08-08T07:10:10.039Z</v>
       </c>
       <c r="F234" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5329,10 +5329,10 @@
         <v>PASS</v>
       </c>
       <c r="D235" t="str">
-        <v>0.94 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-03T18:47:25.864Z</v>
+        <v>2026-08-08T07:10:11.085Z</v>
       </c>
       <c r="F235" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5349,10 +5349,10 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.55 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-03T18:47:26.411Z</v>
+        <v>2026-08-08T07:10:12.078Z</v>
       </c>
       <c r="F236" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5369,10 +5369,10 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>0.92 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-03T18:47:27.332Z</v>
+        <v>2026-08-08T07:10:13.183Z</v>
       </c>
       <c r="F237" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5389,10 +5389,10 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>0.62 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-03T18:47:27.950Z</v>
+        <v>2026-08-08T07:10:13.943Z</v>
       </c>
       <c r="F238" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5409,10 +5409,10 @@
         <v>PASS</v>
       </c>
       <c r="D239" t="str">
-        <v>0.77 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-03T18:47:28.717Z</v>
+        <v>2026-08-08T07:10:14.611Z</v>
       </c>
       <c r="F239" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5429,10 +5429,10 @@
         <v>PASS</v>
       </c>
       <c r="D240" t="str">
-        <v>0.77 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-03T18:47:29.489Z</v>
+        <v>2026-08-08T07:10:15.279Z</v>
       </c>
       <c r="F240" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5449,10 +5449,10 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.84 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-03T18:47:30.332Z</v>
+        <v>2026-08-08T07:10:16.238Z</v>
       </c>
       <c r="F241" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5469,10 +5469,10 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.85 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-03T18:47:31.181Z</v>
+        <v>2026-08-08T07:10:16.950Z</v>
       </c>
       <c r="F242" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5489,10 +5489,10 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.69 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-03T18:47:31.872Z</v>
+        <v>2026-08-08T07:10:18.021Z</v>
       </c>
       <c r="F243" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5509,10 +5509,10 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.77 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-03T18:47:32.645Z</v>
+        <v>2026-08-08T07:10:18.807Z</v>
       </c>
       <c r="F244" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5529,10 +5529,10 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.72 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-03T18:47:33.362Z</v>
+        <v>2026-08-08T07:10:19.611Z</v>
       </c>
       <c r="F245" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5549,10 +5549,10 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.72 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-03T18:47:34.083Z</v>
+        <v>2026-08-08T07:10:20.366Z</v>
       </c>
       <c r="F246" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5569,10 +5569,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.66 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-03T18:47:34.745Z</v>
+        <v>2026-08-08T07:10:21.580Z</v>
       </c>
       <c r="F247" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5589,10 +5589,10 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.89 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-03T18:47:35.634Z</v>
+        <v>2026-08-08T07:10:22.405Z</v>
       </c>
       <c r="F248" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5609,10 +5609,10 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>1.04 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-03T18:47:36.672Z</v>
+        <v>2026-08-08T07:10:23.520Z</v>
       </c>
       <c r="F249" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5629,10 +5629,10 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.92 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-03T18:47:37.591Z</v>
+        <v>2026-08-08T07:10:24.598Z</v>
       </c>
       <c r="F250" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5649,10 +5649,10 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.84 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-03T18:47:38.432Z</v>
+        <v>2026-08-08T07:10:25.377Z</v>
       </c>
       <c r="F251" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5669,10 +5669,10 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.83 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-03T18:47:39.263Z</v>
+        <v>2026-08-08T07:10:26.202Z</v>
       </c>
       <c r="F252" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5689,10 +5689,10 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.65 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-03T18:47:39.914Z</v>
+        <v>2026-08-08T07:10:27.118Z</v>
       </c>
       <c r="F253" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5709,10 +5709,10 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>0.57 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-03T18:47:40.485Z</v>
+        <v>2026-08-08T07:10:28.309Z</v>
       </c>
       <c r="F254" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5729,10 +5729,10 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>0.86 sec</v>
+        <v>1.14 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-03T18:47:41.343Z</v>
+        <v>2026-08-08T07:10:29.444Z</v>
       </c>
       <c r="F255" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5749,10 +5749,10 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>1.02 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-03T18:47:42.361Z</v>
+        <v>2026-08-08T07:10:30.552Z</v>
       </c>
       <c r="F256" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5769,10 +5769,10 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.52 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-03T18:47:42.882Z</v>
+        <v>2026-08-08T07:10:31.356Z</v>
       </c>
       <c r="F257" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5789,10 +5789,10 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>1.01 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-03T18:47:43.888Z</v>
+        <v>2026-08-08T07:10:32.195Z</v>
       </c>
       <c r="F258" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5809,10 +5809,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.65 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-03T18:47:44.536Z</v>
+        <v>2026-08-08T07:10:33.365Z</v>
       </c>
       <c r="F259" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5829,10 +5829,10 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.53 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-03T18:47:45.066Z</v>
+        <v>2026-08-08T07:10:34.307Z</v>
       </c>
       <c r="F260" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5849,10 +5849,10 @@
         <v>PASS</v>
       </c>
       <c r="D261" t="str">
-        <v>0.90 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-03T18:47:45.966Z</v>
+        <v>2026-08-08T07:10:35.427Z</v>
       </c>
       <c r="F261" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5869,10 +5869,10 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.80 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-03T18:47:46.767Z</v>
+        <v>2026-08-08T07:10:36.522Z</v>
       </c>
       <c r="F262" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5889,10 +5889,10 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.71 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-03T18:47:47.478Z</v>
+        <v>2026-08-08T07:10:37.338Z</v>
       </c>
       <c r="F263" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5909,10 +5909,10 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.49 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-03T18:47:47.964Z</v>
+        <v>2026-08-08T07:10:38.142Z</v>
       </c>
       <c r="F264" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5929,10 +5929,10 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.84 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-03T18:47:48.804Z</v>
+        <v>2026-08-08T07:10:39.100Z</v>
       </c>
       <c r="F265" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5949,10 +5949,10 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.61 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-03T18:47:49.416Z</v>
+        <v>2026-08-08T07:10:40.184Z</v>
       </c>
       <c r="F266" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5969,10 +5969,10 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.88 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-03T18:47:50.292Z</v>
+        <v>2026-08-08T07:10:41.112Z</v>
       </c>
       <c r="F267" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -5989,10 +5989,10 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>0.79 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-03T18:47:51.080Z</v>
+        <v>2026-08-08T07:10:42.234Z</v>
       </c>
       <c r="F268" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6009,10 +6009,10 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>0.96 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-03T18:47:52.038Z</v>
+        <v>2026-08-08T07:10:43.081Z</v>
       </c>
       <c r="F269" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6029,10 +6029,10 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>0.54 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-03T18:47:52.579Z</v>
+        <v>2026-08-08T07:10:43.964Z</v>
       </c>
       <c r="F270" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6049,10 +6049,10 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.90 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-03T18:47:53.480Z</v>
+        <v>2026-08-08T07:10:44.936Z</v>
       </c>
       <c r="F271" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6069,10 +6069,10 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.53 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-03T18:47:54.014Z</v>
+        <v>2026-08-08T07:10:45.862Z</v>
       </c>
       <c r="F272" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6089,10 +6089,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.89 sec</v>
+        <v>1.20 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-03T18:47:54.900Z</v>
+        <v>2026-08-08T07:10:47.063Z</v>
       </c>
       <c r="F273" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6109,10 +6109,10 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.80 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-03T18:47:55.696Z</v>
+        <v>2026-08-08T07:10:47.914Z</v>
       </c>
       <c r="F274" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6129,10 +6129,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.93 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-03T18:47:56.626Z</v>
+        <v>2026-08-08T07:10:48.700Z</v>
       </c>
       <c r="F275" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6149,10 +6149,10 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.75 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-03T18:47:57.374Z</v>
+        <v>2026-08-08T07:10:49.492Z</v>
       </c>
       <c r="F276" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6169,10 +6169,10 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>0.84 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-03T18:47:58.217Z</v>
+        <v>2026-08-08T07:10:50.463Z</v>
       </c>
       <c r="F277" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6189,10 +6189,10 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.56 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-03T18:47:58.781Z</v>
+        <v>2026-08-08T07:10:51.324Z</v>
       </c>
       <c r="F278" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6209,10 +6209,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.71 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-03T18:47:59.488Z</v>
+        <v>2026-08-08T07:10:52.298Z</v>
       </c>
       <c r="F279" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6229,10 +6229,10 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.81 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-03T18:48:00.294Z</v>
+        <v>2026-08-08T07:10:53.158Z</v>
       </c>
       <c r="F280" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6249,10 +6249,10 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>1.02 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-03T18:48:01.317Z</v>
+        <v>2026-08-08T07:10:54.018Z</v>
       </c>
       <c r="F281" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6269,10 +6269,10 @@
         <v>PASS</v>
       </c>
       <c r="D282" t="str">
-        <v>0.92 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-03T18:48:02.238Z</v>
+        <v>2026-08-08T07:10:54.793Z</v>
       </c>
       <c r="F282" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6289,10 +6289,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>1.03 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-03T18:48:03.267Z</v>
+        <v>2026-08-08T07:10:55.784Z</v>
       </c>
       <c r="F283" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6309,10 +6309,10 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.90 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-03T18:48:04.167Z</v>
+        <v>2026-08-08T07:10:56.644Z</v>
       </c>
       <c r="F284" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6329,10 +6329,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>1.08 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-03T18:48:05.249Z</v>
+        <v>2026-08-08T07:10:57.602Z</v>
       </c>
       <c r="F285" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6349,10 +6349,10 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>0.71 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-03T18:48:05.961Z</v>
+        <v>2026-08-08T07:10:58.684Z</v>
       </c>
       <c r="F286" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6369,10 +6369,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.95 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-03T18:48:06.909Z</v>
+        <v>2026-08-08T07:10:59.546Z</v>
       </c>
       <c r="F287" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6389,10 +6389,10 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.64 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-03T18:48:07.552Z</v>
+        <v>2026-08-08T07:11:00.337Z</v>
       </c>
       <c r="F288" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6409,10 +6409,10 @@
         <v>PASS</v>
       </c>
       <c r="D289" t="str">
-        <v>1.07 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-03T18:48:08.626Z</v>
+        <v>2026-08-08T07:11:01.547Z</v>
       </c>
       <c r="F289" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6429,10 +6429,10 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>1.07 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-03T18:48:09.692Z</v>
+        <v>2026-08-08T07:11:02.481Z</v>
       </c>
       <c r="F290" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6449,10 +6449,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>1.09 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-03T18:48:10.781Z</v>
+        <v>2026-08-08T07:11:03.409Z</v>
       </c>
       <c r="F291" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6469,10 +6469,10 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>1.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-03T18:48:11.784Z</v>
+        <v>2026-08-08T07:11:04.339Z</v>
       </c>
       <c r="F292" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6489,10 +6489,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.73 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-03T18:48:12.515Z</v>
+        <v>2026-08-08T07:11:05.160Z</v>
       </c>
       <c r="F293" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6509,10 +6509,10 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>1.14 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-03T18:48:13.651Z</v>
+        <v>2026-08-08T07:11:05.918Z</v>
       </c>
       <c r="F294" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6529,10 +6529,10 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>1.39 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-03T18:48:15.045Z</v>
+        <v>2026-08-08T07:11:06.976Z</v>
       </c>
       <c r="F295" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6549,10 +6549,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>1.03 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-03T18:48:16.075Z</v>
+        <v>2026-08-08T07:11:07.981Z</v>
       </c>
       <c r="F296" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6569,10 +6569,10 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>1.23 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-03T18:48:17.305Z</v>
+        <v>2026-08-08T07:11:08.919Z</v>
       </c>
       <c r="F297" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6589,10 +6589,10 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>0.94 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-03T18:48:18.248Z</v>
+        <v>2026-08-08T07:11:09.752Z</v>
       </c>
       <c r="F298" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6609,10 +6609,10 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.89 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-03T18:48:19.137Z</v>
+        <v>2026-08-08T07:11:10.510Z</v>
       </c>
       <c r="F299" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6629,10 +6629,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>1.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-03T18:48:20.134Z</v>
+        <v>2026-08-08T07:11:11.282Z</v>
       </c>
       <c r="F300" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6649,10 +6649,10 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>1.35 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-03T18:48:21.484Z</v>
+        <v>2026-08-08T07:11:12.215Z</v>
       </c>
       <c r="F301" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6669,10 +6669,10 @@
         <v>PASS</v>
       </c>
       <c r="D302" t="str">
-        <v>0.97 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-03T18:48:22.459Z</v>
+        <v>2026-08-08T07:11:13.041Z</v>
       </c>
       <c r="F302" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6689,10 +6689,10 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>0.92 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-03T18:48:23.380Z</v>
+        <v>2026-08-08T07:11:14.152Z</v>
       </c>
       <c r="F303" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6709,10 +6709,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.80 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-03T18:48:24.179Z</v>
+        <v>2026-08-08T07:11:15.043Z</v>
       </c>
       <c r="F304" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6729,10 +6729,10 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.70 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-03T18:48:24.879Z</v>
+        <v>2026-08-08T07:11:16.023Z</v>
       </c>
       <c r="F305" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6749,10 +6749,10 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.81 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-03T18:48:25.684Z</v>
+        <v>2026-08-08T07:11:16.781Z</v>
       </c>
       <c r="F306" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6769,10 +6769,10 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>0.92 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-03T18:48:26.606Z</v>
+        <v>2026-08-08T07:11:17.784Z</v>
       </c>
       <c r="F307" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6789,10 +6789,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.59 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-03T18:48:27.196Z</v>
+        <v>2026-08-08T07:11:18.700Z</v>
       </c>
       <c r="F308" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6809,10 +6809,10 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.74 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-03T18:48:27.941Z</v>
+        <v>2026-08-08T07:11:19.623Z</v>
       </c>
       <c r="F309" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6829,10 +6829,10 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>1.03 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-03T18:48:28.973Z</v>
+        <v>2026-08-08T07:11:20.580Z</v>
       </c>
       <c r="F310" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6849,10 +6849,10 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.54 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-03T18:48:29.512Z</v>
+        <v>2026-08-08T07:11:21.433Z</v>
       </c>
       <c r="F311" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6869,10 +6869,10 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.49 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-03T18:48:30.000Z</v>
+        <v>2026-08-08T07:11:22.299Z</v>
       </c>
       <c r="F312" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6889,10 +6889,10 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.88 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-03T18:48:30.883Z</v>
+        <v>2026-08-08T07:11:23.253Z</v>
       </c>
       <c r="F313" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6909,10 +6909,10 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.57 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-03T18:48:31.457Z</v>
+        <v>2026-08-08T07:11:24.169Z</v>
       </c>
       <c r="F314" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6929,10 +6929,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.97 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-03T18:48:32.425Z</v>
+        <v>2026-08-08T07:11:25.130Z</v>
       </c>
       <c r="F315" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6949,10 +6949,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.82 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-03T18:48:33.241Z</v>
+        <v>2026-08-08T07:11:25.993Z</v>
       </c>
       <c r="F316" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6969,10 +6969,10 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.75 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-03T18:48:33.989Z</v>
+        <v>2026-08-08T07:11:26.761Z</v>
       </c>
       <c r="F317" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -6989,10 +6989,10 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.78 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-03T18:48:34.769Z</v>
+        <v>2026-08-08T07:11:27.483Z</v>
       </c>
       <c r="F318" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7009,10 +7009,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>1.10 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-03T18:48:35.867Z</v>
+        <v>2026-08-08T07:11:28.484Z</v>
       </c>
       <c r="F319" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7029,10 +7029,10 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>1.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-03T18:48:36.872Z</v>
+        <v>2026-08-08T07:11:29.399Z</v>
       </c>
       <c r="F320" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7049,10 +7049,10 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>0.83 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-03T18:48:37.700Z</v>
+        <v>2026-08-08T07:11:30.319Z</v>
       </c>
       <c r="F321" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7069,10 +7069,10 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.83 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-03T18:48:38.529Z</v>
+        <v>2026-08-08T07:11:31.221Z</v>
       </c>
       <c r="F322" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7089,10 +7089,10 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.75 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-03T18:48:39.281Z</v>
+        <v>2026-08-08T07:11:31.998Z</v>
       </c>
       <c r="F323" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7109,10 +7109,10 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.78 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-03T18:48:40.065Z</v>
+        <v>2026-08-08T07:11:32.768Z</v>
       </c>
       <c r="F324" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7129,10 +7129,10 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>1.51 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-03T18:48:41.578Z</v>
+        <v>2026-08-08T07:11:33.735Z</v>
       </c>
       <c r="F325" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7149,10 +7149,10 @@
         <v>PASS</v>
       </c>
       <c r="D326" t="str">
-        <v>0.83 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-03T18:48:42.411Z</v>
+        <v>2026-08-08T07:11:34.632Z</v>
       </c>
       <c r="F326" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7169,10 +7169,10 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.91 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-03T18:48:43.318Z</v>
+        <v>2026-08-08T07:11:35.571Z</v>
       </c>
       <c r="F327" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7189,10 +7189,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.64 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-03T18:48:43.954Z</v>
+        <v>2026-08-08T07:11:36.451Z</v>
       </c>
       <c r="F328" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7209,10 +7209,10 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>0.79 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-03T18:48:44.741Z</v>
+        <v>2026-08-08T07:11:37.255Z</v>
       </c>
       <c r="F329" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7229,10 +7229,10 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.86 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-03T18:48:45.600Z</v>
+        <v>2026-08-08T07:11:38.097Z</v>
       </c>
       <c r="F330" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7249,10 +7249,10 @@
         <v>PASS</v>
       </c>
       <c r="D331" t="str">
-        <v>0.73 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-03T18:48:46.335Z</v>
+        <v>2026-08-08T07:11:39.102Z</v>
       </c>
       <c r="F331" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7269,10 +7269,10 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.73 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-03T18:48:47.068Z</v>
+        <v>2026-08-08T07:11:40.066Z</v>
       </c>
       <c r="F332" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7292,7 +7292,7 @@
         <v>0.98 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-03T18:48:48.046Z</v>
+        <v>2026-08-08T07:11:41.045Z</v>
       </c>
       <c r="F333" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7309,10 +7309,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.69 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-03T18:48:48.741Z</v>
+        <v>2026-08-08T07:11:41.956Z</v>
       </c>
       <c r="F334" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7329,10 +7329,10 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>0.67 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-03T18:48:49.413Z</v>
+        <v>2026-08-08T07:11:42.769Z</v>
       </c>
       <c r="F335" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7349,10 +7349,10 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.77 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-03T18:48:50.182Z</v>
+        <v>2026-08-08T07:11:43.587Z</v>
       </c>
       <c r="F336" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7369,10 +7369,10 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.88 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-03T18:48:51.065Z</v>
+        <v>2026-08-08T07:11:44.488Z</v>
       </c>
       <c r="F337" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7389,10 +7389,10 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>1.05 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-03T18:48:52.113Z</v>
+        <v>2026-08-08T07:11:45.316Z</v>
       </c>
       <c r="F338" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7409,10 +7409,10 @@
         <v>PASS</v>
       </c>
       <c r="D339" t="str">
-        <v>1.15 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-03T18:48:53.264Z</v>
+        <v>2026-08-08T07:11:46.436Z</v>
       </c>
       <c r="F339" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7429,10 +7429,10 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>1.01 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-03T18:48:54.270Z</v>
+        <v>2026-08-08T07:11:47.274Z</v>
       </c>
       <c r="F340" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7449,10 +7449,10 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.92 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-03T18:48:55.191Z</v>
+        <v>2026-08-08T07:11:48.094Z</v>
       </c>
       <c r="F341" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7469,10 +7469,10 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>1.02 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-03T18:48:56.213Z</v>
+        <v>2026-08-08T07:11:49.097Z</v>
       </c>
       <c r="F342" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7489,10 +7489,10 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>1.06 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-03T18:48:57.278Z</v>
+        <v>2026-08-08T07:11:50.141Z</v>
       </c>
       <c r="F343" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7509,10 +7509,10 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.99 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-03T18:48:58.266Z</v>
+        <v>2026-08-08T07:11:50.984Z</v>
       </c>
       <c r="F344" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7529,10 +7529,10 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>1.05 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-03T18:48:59.318Z</v>
+        <v>2026-08-08T07:11:51.924Z</v>
       </c>
       <c r="F345" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7549,10 +7549,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.93 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-03T18:49:00.248Z</v>
+        <v>2026-08-08T07:11:52.771Z</v>
       </c>
       <c r="F346" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7569,10 +7569,10 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.90 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-03T18:49:01.151Z</v>
+        <v>2026-08-08T07:11:53.582Z</v>
       </c>
       <c r="F347" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7589,10 +7589,10 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.73 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-03T18:49:01.882Z</v>
+        <v>2026-08-08T07:11:54.406Z</v>
       </c>
       <c r="F348" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7609,10 +7609,10 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>1.12 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-03T18:49:03.005Z</v>
+        <v>2026-08-08T07:11:55.475Z</v>
       </c>
       <c r="F349" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7629,10 +7629,10 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.92 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-03T18:49:03.921Z</v>
+        <v>2026-08-08T07:11:56.352Z</v>
       </c>
       <c r="F350" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7649,10 +7649,10 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>0.99 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-03T18:49:04.911Z</v>
+        <v>2026-08-08T07:11:57.562Z</v>
       </c>
       <c r="F351" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7672,7 +7672,7 @@
         <v>0.90 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-03T18:49:05.806Z</v>
+        <v>2026-08-08T07:11:58.461Z</v>
       </c>
       <c r="F352" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7689,10 +7689,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.62 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-03T18:49:06.424Z</v>
+        <v>2026-08-08T07:11:59.308Z</v>
       </c>
       <c r="F353" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7709,10 +7709,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.82 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-03T18:49:07.241Z</v>
+        <v>2026-08-08T07:12:00.144Z</v>
       </c>
       <c r="F354" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7729,10 +7729,10 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>1.03 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-03T18:49:08.276Z</v>
+        <v>2026-08-08T07:12:01.118Z</v>
       </c>
       <c r="F355" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7749,10 +7749,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.91 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-03T18:49:09.189Z</v>
+        <v>2026-08-08T07:12:02.199Z</v>
       </c>
       <c r="F356" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7769,10 +7769,10 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>1.05 sec</v>
+        <v>1.22 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-03T18:49:10.241Z</v>
+        <v>2026-08-08T07:12:03.417Z</v>
       </c>
       <c r="F357" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7789,10 +7789,10 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>1.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-03T18:49:11.239Z</v>
+        <v>2026-08-08T07:12:04.213Z</v>
       </c>
       <c r="F358" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7809,10 +7809,10 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>0.92 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-03T18:49:12.159Z</v>
+        <v>2026-08-08T07:12:05.069Z</v>
       </c>
       <c r="F359" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7829,10 +7829,10 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>0.63 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-03T18:49:12.789Z</v>
+        <v>2026-08-08T07:12:05.838Z</v>
       </c>
       <c r="F360" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7849,10 +7849,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>1.02 sec</v>
+        <v>1.24 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-03T18:49:13.813Z</v>
+        <v>2026-08-08T07:12:07.080Z</v>
       </c>
       <c r="F361" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7869,10 +7869,10 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.95 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-03T18:49:14.768Z</v>
+        <v>2026-08-08T07:12:07.908Z</v>
       </c>
       <c r="F362" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7889,10 +7889,10 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>1.11 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-03T18:49:15.881Z</v>
+        <v>2026-08-08T07:12:08.917Z</v>
       </c>
       <c r="F363" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7909,10 +7909,10 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>1.02 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-03T18:49:16.898Z</v>
+        <v>2026-08-08T07:12:09.881Z</v>
       </c>
       <c r="F364" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7929,10 +7929,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.76 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-03T18:49:17.661Z</v>
+        <v>2026-08-08T07:12:10.699Z</v>
       </c>
       <c r="F365" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7949,10 +7949,10 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.89 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-03T18:49:18.550Z</v>
+        <v>2026-08-08T07:12:11.491Z</v>
       </c>
       <c r="F366" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7969,10 +7969,10 @@
         <v>PASS</v>
       </c>
       <c r="D367" t="str">
-        <v>1.08 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-03T18:49:19.632Z</v>
+        <v>2026-08-08T07:12:12.554Z</v>
       </c>
       <c r="F367" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -7989,10 +7989,10 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.90 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-03T18:49:20.532Z</v>
+        <v>2026-08-08T07:12:13.550Z</v>
       </c>
       <c r="F368" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8009,10 +8009,10 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>1.01 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-03T18:49:21.543Z</v>
+        <v>2026-08-08T07:12:14.486Z</v>
       </c>
       <c r="F369" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8029,10 +8029,10 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>0.71 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-03T18:49:22.254Z</v>
+        <v>2026-08-08T07:12:15.351Z</v>
       </c>
       <c r="F370" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8049,10 +8049,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.62 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-03T18:49:22.873Z</v>
+        <v>2026-08-08T07:12:16.211Z</v>
       </c>
       <c r="F371" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8072,7 +8072,7 @@
         <v>0.90 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-03T18:49:23.774Z</v>
+        <v>2026-08-08T07:12:17.115Z</v>
       </c>
       <c r="F372" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8089,10 +8089,10 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.73 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-03T18:49:24.504Z</v>
+        <v>2026-08-08T07:12:18.111Z</v>
       </c>
       <c r="F373" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8109,10 +8109,10 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.81 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-03T18:49:25.310Z</v>
+        <v>2026-08-08T07:12:19.060Z</v>
       </c>
       <c r="F374" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8129,10 +8129,10 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>1.04 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-03T18:49:26.354Z</v>
+        <v>2026-08-08T07:12:20.010Z</v>
       </c>
       <c r="F375" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8149,10 +8149,10 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>0.68 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-03T18:49:27.031Z</v>
+        <v>2026-08-08T07:12:21.113Z</v>
       </c>
       <c r="F376" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8169,10 +8169,10 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.68 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-03T18:49:27.712Z</v>
+        <v>2026-08-08T07:12:21.901Z</v>
       </c>
       <c r="F377" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8189,10 +8189,10 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>0.71 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-03T18:49:28.425Z</v>
+        <v>2026-08-08T07:12:22.908Z</v>
       </c>
       <c r="F378" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8209,10 +8209,10 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.98 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-03T18:49:29.408Z</v>
+        <v>2026-08-08T07:12:23.882Z</v>
       </c>
       <c r="F379" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8229,10 +8229,10 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>0.69 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-03T18:49:30.093Z</v>
+        <v>2026-08-08T07:12:24.749Z</v>
       </c>
       <c r="F380" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8249,10 +8249,10 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.91 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-03T18:49:31.005Z</v>
+        <v>2026-08-08T07:12:25.676Z</v>
       </c>
       <c r="F381" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8269,10 +8269,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>1.07 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-03T18:49:32.073Z</v>
+        <v>2026-08-08T07:12:26.551Z</v>
       </c>
       <c r="F382" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8289,10 +8289,10 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>1.08 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-03T18:49:33.149Z</v>
+        <v>2026-08-08T07:12:27.317Z</v>
       </c>
       <c r="F383" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8309,10 +8309,10 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.94 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-03T18:49:34.091Z</v>
+        <v>2026-08-08T07:12:28.111Z</v>
       </c>
       <c r="F384" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8329,10 +8329,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>1.23 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-03T18:49:35.317Z</v>
+        <v>2026-08-08T07:12:29.232Z</v>
       </c>
       <c r="F385" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8349,10 +8349,10 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>1.01 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-03T18:49:36.332Z</v>
+        <v>2026-08-08T07:12:30.340Z</v>
       </c>
       <c r="F386" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8369,10 +8369,10 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>1.06 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-03T18:49:37.390Z</v>
+        <v>2026-08-08T07:12:31.359Z</v>
       </c>
       <c r="F387" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8389,10 +8389,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.95 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-03T18:49:38.343Z</v>
+        <v>2026-08-08T07:12:32.303Z</v>
       </c>
       <c r="F388" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8409,10 +8409,10 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.64 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-03T18:49:38.983Z</v>
+        <v>2026-08-08T07:12:33.094Z</v>
       </c>
       <c r="F389" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8429,10 +8429,10 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>1.10 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-03T18:49:40.080Z</v>
+        <v>2026-08-08T07:12:33.873Z</v>
       </c>
       <c r="F390" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8449,10 +8449,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>1.06 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-03T18:49:41.144Z</v>
+        <v>2026-08-08T07:12:34.854Z</v>
       </c>
       <c r="F391" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8469,10 +8469,10 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>0.65 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-03T18:49:41.794Z</v>
+        <v>2026-08-08T07:12:36.009Z</v>
       </c>
       <c r="F392" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8489,10 +8489,10 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>0.81 sec</v>
+        <v>1.26 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-03T18:49:42.601Z</v>
+        <v>2026-08-08T07:12:37.269Z</v>
       </c>
       <c r="F393" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8509,10 +8509,10 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.68 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-03T18:49:43.279Z</v>
+        <v>2026-08-08T07:12:38.317Z</v>
       </c>
       <c r="F394" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8529,10 +8529,10 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.85 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-03T18:49:44.127Z</v>
+        <v>2026-08-08T07:12:39.135Z</v>
       </c>
       <c r="F395" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8549,10 +8549,10 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>0.60 sec</v>
+        <v>0.63 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-03T18:49:44.724Z</v>
+        <v>2026-08-08T07:12:39.763Z</v>
       </c>
       <c r="F396" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8569,10 +8569,10 @@
         <v>PASS</v>
       </c>
       <c r="D397" t="str">
-        <v>1.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-03T18:49:45.727Z</v>
+        <v>2026-08-08T07:12:40.563Z</v>
       </c>
       <c r="F397" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8589,10 +8589,10 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>1.10 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-03T18:49:46.827Z</v>
+        <v>2026-08-08T07:12:41.561Z</v>
       </c>
       <c r="F398" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8609,10 +8609,10 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>1.03 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-03T18:49:47.860Z</v>
+        <v>2026-08-08T07:12:42.770Z</v>
       </c>
       <c r="F399" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8629,10 +8629,10 @@
         <v>PASS</v>
       </c>
       <c r="D400" t="str">
-        <v>0.68 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-03T18:49:48.537Z</v>
+        <v>2026-08-08T07:12:43.712Z</v>
       </c>
       <c r="F400" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8649,10 +8649,10 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.89 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-03T18:49:49.424Z</v>
+        <v>2026-08-08T07:12:44.549Z</v>
       </c>
       <c r="F401" t="str">
         <v>Too many requests from this IP, please try again later.</v>
@@ -8711,7 +8711,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-01T10:49:38.258Z</v>
+        <v>2026-08-08T07:13:18.018Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -8728,10 +8728,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-01T10:49:38.275Z</v>
+        <v>2026-08-08T07:13:18.023Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -8751,7 +8751,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-01T10:49:38.290Z</v>
+        <v>2026-08-08T07:13:18.028Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -8768,10 +8768,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-01T10:49:38.306Z</v>
+        <v>2026-08-08T07:13:18.040Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -8791,7 +8791,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-01T10:49:38.322Z</v>
+        <v>2026-08-08T07:13:18.059Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -8808,10 +8808,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-01T10:49:38.338Z</v>
+        <v>2026-08-08T07:13:18.074Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -8828,10 +8828,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-01T10:49:38.353Z</v>
+        <v>2026-08-08T07:13:18.090Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -8851,7 +8851,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-01T10:49:38.369Z</v>
+        <v>2026-08-08T07:13:18.106Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -8871,7 +8871,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-01T10:49:38.385Z</v>
+        <v>2026-08-08T07:13:18.122Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -8891,7 +8891,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-01T10:49:38.400Z</v>
+        <v>2026-08-08T07:13:18.137Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -8911,7 +8911,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-01T10:49:38.415Z</v>
+        <v>2026-08-08T07:13:18.153Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -8931,7 +8931,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-01T10:49:38.432Z</v>
+        <v>2026-08-08T07:13:18.169Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -8948,10 +8948,10 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-01T10:49:38.448Z</v>
+        <v>2026-08-08T07:13:18.184Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -8968,10 +8968,10 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-01T10:49:38.463Z</v>
+        <v>2026-08-08T07:13:18.200Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -8991,7 +8991,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-01T10:49:38.477Z</v>
+        <v>2026-08-08T07:13:18.215Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -9011,7 +9011,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-01T10:49:38.493Z</v>
+        <v>2026-08-08T07:13:18.231Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -9028,10 +9028,10 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-01T10:49:38.509Z</v>
+        <v>2026-08-08T07:13:18.246Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -9048,10 +9048,10 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-01T10:49:38.524Z</v>
+        <v>2026-08-08T07:13:18.262Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -9068,10 +9068,10 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-01T10:49:38.539Z</v>
+        <v>2026-08-08T07:13:18.278Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -9091,7 +9091,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-01T10:49:38.555Z</v>
+        <v>2026-08-08T07:13:18.294Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -9108,10 +9108,10 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-01T10:49:38.570Z</v>
+        <v>2026-08-08T07:13:18.310Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -9128,10 +9128,10 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-01T10:49:38.586Z</v>
+        <v>2026-08-08T07:13:18.325Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -9151,7 +9151,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-01T10:49:38.602Z</v>
+        <v>2026-08-08T07:13:18.341Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -9171,7 +9171,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-01T10:49:38.618Z</v>
+        <v>2026-08-08T07:13:18.357Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -9188,10 +9188,10 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-01T10:49:38.633Z</v>
+        <v>2026-08-08T07:13:18.373Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -9211,7 +9211,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-01T10:49:38.649Z</v>
+        <v>2026-08-08T07:13:18.389Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -9231,7 +9231,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-01T10:49:38.664Z</v>
+        <v>2026-08-08T07:13:18.404Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -9248,10 +9248,10 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-01T10:49:38.679Z</v>
+        <v>2026-08-08T07:13:18.420Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -9271,7 +9271,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-01T10:49:38.695Z</v>
+        <v>2026-08-08T07:13:18.436Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -9288,10 +9288,10 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-01T10:49:38.710Z</v>
+        <v>2026-08-08T07:13:18.452Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -9308,10 +9308,10 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-01T10:49:38.726Z</v>
+        <v>2026-08-08T07:13:18.468Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -9328,10 +9328,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-01T10:49:38.741Z</v>
+        <v>2026-08-08T07:13:18.484Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -9351,7 +9351,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-01T10:49:38.758Z</v>
+        <v>2026-08-08T07:13:18.500Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -9368,10 +9368,10 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-01T10:49:38.773Z</v>
+        <v>2026-08-08T07:13:18.516Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -9388,10 +9388,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-01T10:49:38.788Z</v>
+        <v>2026-08-08T07:13:18.532Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -9408,10 +9408,10 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-01T10:49:38.804Z</v>
+        <v>2026-08-08T07:13:18.547Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -9431,7 +9431,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-01T10:49:38.820Z</v>
+        <v>2026-08-08T07:13:18.563Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -9448,10 +9448,10 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-01T10:49:38.835Z</v>
+        <v>2026-08-08T07:13:18.579Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -9471,7 +9471,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-01T10:49:38.850Z</v>
+        <v>2026-08-08T07:13:18.594Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -9488,10 +9488,10 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-01T10:49:38.867Z</v>
+        <v>2026-08-08T07:13:18.609Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -9508,10 +9508,10 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-01T10:49:38.883Z</v>
+        <v>2026-08-08T07:13:18.625Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -9528,10 +9528,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-01T10:49:38.899Z</v>
+        <v>2026-08-08T07:13:18.640Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -9548,10 +9548,10 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-01T10:49:38.913Z</v>
+        <v>2026-08-08T07:13:18.656Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -9568,10 +9568,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-01T10:49:38.929Z</v>
+        <v>2026-08-08T07:13:18.671Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -9591,7 +9591,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-01T10:49:38.945Z</v>
+        <v>2026-08-08T07:13:18.687Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -9611,7 +9611,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-01T10:49:38.960Z</v>
+        <v>2026-08-08T07:13:18.702Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -9631,7 +9631,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-01T10:49:38.976Z</v>
+        <v>2026-08-08T07:13:18.718Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -9651,7 +9651,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-01T10:49:38.991Z</v>
+        <v>2026-08-08T07:13:18.733Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -9671,7 +9671,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-01T10:49:39.007Z</v>
+        <v>2026-08-08T07:13:18.750Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -9688,10 +9688,10 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-01T10:49:39.023Z</v>
+        <v>2026-08-08T07:13:18.765Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -9711,7 +9711,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-01T10:49:39.038Z</v>
+        <v>2026-08-08T07:13:18.781Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -9731,7 +9731,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-01T10:49:39.054Z</v>
+        <v>2026-08-08T07:13:18.797Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -9751,7 +9751,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-01T10:49:39.070Z</v>
+        <v>2026-08-08T07:13:18.814Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -9768,10 +9768,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-01T10:49:39.086Z</v>
+        <v>2026-08-08T07:13:18.828Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -9788,10 +9788,10 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-01T10:49:39.101Z</v>
+        <v>2026-08-08T07:13:18.844Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -9808,10 +9808,10 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-01T10:49:39.117Z</v>
+        <v>2026-08-08T07:13:18.859Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -9828,10 +9828,10 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-01T10:49:39.132Z</v>
+        <v>2026-08-08T07:13:18.875Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -9851,7 +9851,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-01T10:49:39.147Z</v>
+        <v>2026-08-08T07:13:18.890Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -9868,10 +9868,10 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-01T10:49:39.162Z</v>
+        <v>2026-08-08T07:13:18.906Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -9888,10 +9888,10 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-01T10:49:39.177Z</v>
+        <v>2026-08-08T07:13:18.922Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -9908,10 +9908,10 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-01T10:49:39.193Z</v>
+        <v>2026-08-08T07:13:18.938Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -9928,10 +9928,10 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-01T10:49:39.209Z</v>
+        <v>2026-08-08T07:13:18.954Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -9948,10 +9948,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-01T10:49:39.225Z</v>
+        <v>2026-08-08T07:13:18.969Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -9968,10 +9968,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-01T10:49:39.240Z</v>
+        <v>2026-08-08T07:13:18.985Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -9991,7 +9991,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-01T10:49:39.255Z</v>
+        <v>2026-08-08T07:13:19.000Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -10011,7 +10011,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-01T10:49:39.271Z</v>
+        <v>2026-08-08T07:13:19.015Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -10031,7 +10031,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-01T10:49:39.287Z</v>
+        <v>2026-08-08T07:13:19.031Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -10051,7 +10051,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-01T10:49:39.303Z</v>
+        <v>2026-08-08T07:13:19.047Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -10068,10 +10068,10 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-01T10:49:39.318Z</v>
+        <v>2026-08-08T07:13:19.063Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -10091,7 +10091,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-01T10:49:39.334Z</v>
+        <v>2026-08-08T07:13:19.079Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -10108,10 +10108,10 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-01T10:49:39.348Z</v>
+        <v>2026-08-08T07:13:19.095Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -10128,10 +10128,10 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-01T10:49:39.364Z</v>
+        <v>2026-08-08T07:13:19.110Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -10148,10 +10148,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-01T10:49:39.380Z</v>
+        <v>2026-08-08T07:13:19.125Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -10171,7 +10171,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-01T10:49:39.396Z</v>
+        <v>2026-08-08T07:13:19.141Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -10191,7 +10191,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-01T10:49:39.411Z</v>
+        <v>2026-08-08T07:13:19.156Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -10211,7 +10211,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-01T10:49:39.427Z</v>
+        <v>2026-08-08T07:13:19.172Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -10228,10 +10228,10 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-01T10:49:39.443Z</v>
+        <v>2026-08-08T07:13:19.187Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -10251,7 +10251,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-01T10:49:39.459Z</v>
+        <v>2026-08-08T07:13:19.203Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -10271,7 +10271,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-01T10:49:39.474Z</v>
+        <v>2026-08-08T07:13:19.218Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -10291,7 +10291,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-01T10:49:39.490Z</v>
+        <v>2026-08-08T07:13:19.234Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -10311,7 +10311,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-01T10:49:39.505Z</v>
+        <v>2026-08-08T07:13:19.249Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -10331,7 +10331,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-01T10:49:39.522Z</v>
+        <v>2026-08-08T07:13:19.265Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -10351,7 +10351,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-01T10:49:39.537Z</v>
+        <v>2026-08-08T07:13:19.280Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -10368,10 +10368,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-01T10:49:39.552Z</v>
+        <v>2026-08-08T07:13:19.296Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -10391,7 +10391,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-01T10:49:39.569Z</v>
+        <v>2026-08-08T07:13:19.312Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -10411,7 +10411,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-01T10:49:39.583Z</v>
+        <v>2026-08-08T07:13:19.327Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -10431,7 +10431,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-01T10:49:39.599Z</v>
+        <v>2026-08-08T07:13:19.343Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -10451,7 +10451,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-01T10:49:39.614Z</v>
+        <v>2026-08-08T07:13:19.358Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -10471,7 +10471,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-01T10:49:39.631Z</v>
+        <v>2026-08-08T07:13:19.374Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -10491,7 +10491,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-01T10:49:39.646Z</v>
+        <v>2026-08-08T07:13:19.389Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -10511,7 +10511,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-01T10:49:39.661Z</v>
+        <v>2026-08-08T07:13:19.405Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -10531,7 +10531,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-01T10:49:39.677Z</v>
+        <v>2026-08-08T07:13:19.422Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -10551,7 +10551,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-01T10:49:39.693Z</v>
+        <v>2026-08-08T07:13:19.438Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -10568,10 +10568,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-01T10:49:39.707Z</v>
+        <v>2026-08-08T07:13:19.454Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -10588,10 +10588,10 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-01T10:49:39.723Z</v>
+        <v>2026-08-08T07:13:19.469Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -10611,7 +10611,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-01T10:49:39.738Z</v>
+        <v>2026-08-08T07:13:19.484Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -10628,10 +10628,10 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-01T10:49:39.754Z</v>
+        <v>2026-08-08T07:13:19.500Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -10648,10 +10648,10 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-01T10:49:39.770Z</v>
+        <v>2026-08-08T07:13:19.515Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -10668,10 +10668,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-01T10:49:39.785Z</v>
+        <v>2026-08-08T07:13:19.531Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -10691,7 +10691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-01T10:49:39.800Z</v>
+        <v>2026-08-08T07:13:19.546Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -10708,10 +10708,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-01T10:49:39.816Z</v>
+        <v>2026-08-08T07:13:19.561Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -10728,10 +10728,10 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-01T10:49:39.831Z</v>
+        <v>2026-08-08T07:13:19.577Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -10751,7 +10751,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-01T10:49:39.847Z</v>
+        <v>2026-08-08T07:13:19.593Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -10768,10 +10768,10 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-01T10:49:39.863Z</v>
+        <v>2026-08-08T07:13:19.608Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -10788,10 +10788,10 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-01T10:49:39.878Z</v>
+        <v>2026-08-08T07:13:19.624Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -10811,7 +10811,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-01T10:49:39.894Z</v>
+        <v>2026-08-08T07:13:19.640Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -10831,7 +10831,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-01T10:49:39.909Z</v>
+        <v>2026-08-08T07:13:19.655Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -10851,7 +10851,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-01T10:49:39.924Z</v>
+        <v>2026-08-08T07:13:19.670Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -10871,7 +10871,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-01T10:49:39.940Z</v>
+        <v>2026-08-08T07:13:19.686Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -10891,7 +10891,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-01T10:49:39.955Z</v>
+        <v>2026-08-08T07:13:19.701Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -10911,7 +10911,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-01T10:49:39.970Z</v>
+        <v>2026-08-08T07:13:19.717Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -10928,10 +10928,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-01T10:49:39.986Z</v>
+        <v>2026-08-08T07:13:19.733Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -10948,10 +10948,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-01T10:49:40.002Z</v>
+        <v>2026-08-08T07:13:19.748Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -10971,7 +10971,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-01T10:49:40.018Z</v>
+        <v>2026-08-08T07:13:19.764Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -10991,7 +10991,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-01T10:49:40.034Z</v>
+        <v>2026-08-08T07:13:19.780Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -11011,7 +11011,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-01T10:49:40.050Z</v>
+        <v>2026-08-08T07:13:19.796Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -11028,10 +11028,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-01T10:49:40.066Z</v>
+        <v>2026-08-08T07:13:19.812Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -11051,7 +11051,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-01T10:49:40.081Z</v>
+        <v>2026-08-08T07:13:19.827Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -11068,10 +11068,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-01T10:49:40.097Z</v>
+        <v>2026-08-08T07:13:19.842Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -11088,10 +11088,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-01T10:49:40.112Z</v>
+        <v>2026-08-08T07:13:19.858Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -11108,10 +11108,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-01T10:49:40.128Z</v>
+        <v>2026-08-08T07:13:19.873Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -11131,7 +11131,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-01T10:49:40.144Z</v>
+        <v>2026-08-08T07:13:19.889Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -11148,10 +11148,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-01T10:49:40.159Z</v>
+        <v>2026-08-08T07:13:19.905Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -11171,7 +11171,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-01T10:49:40.175Z</v>
+        <v>2026-08-08T07:13:19.921Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -11188,10 +11188,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-01T10:49:40.191Z</v>
+        <v>2026-08-08T07:13:19.936Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -11211,7 +11211,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-01T10:49:40.206Z</v>
+        <v>2026-08-08T07:13:19.951Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -11231,7 +11231,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-01T10:49:40.221Z</v>
+        <v>2026-08-08T07:13:19.967Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -11251,7 +11251,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-01T10:49:40.237Z</v>
+        <v>2026-08-08T07:13:19.983Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -11268,10 +11268,10 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-01T10:49:40.252Z</v>
+        <v>2026-08-08T07:13:19.999Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -11288,10 +11288,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-01T10:49:40.268Z</v>
+        <v>2026-08-08T07:13:20.013Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -11311,7 +11311,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-01T10:49:40.283Z</v>
+        <v>2026-08-08T07:13:20.029Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -11328,10 +11328,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-01T10:49:40.299Z</v>
+        <v>2026-08-08T07:13:20.044Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -11351,7 +11351,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-01T10:49:40.315Z</v>
+        <v>2026-08-08T07:13:20.060Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -11368,10 +11368,10 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-01T10:49:40.330Z</v>
+        <v>2026-08-08T07:13:20.077Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -11391,7 +11391,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-01T10:49:40.345Z</v>
+        <v>2026-08-08T07:13:20.092Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -11408,10 +11408,10 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-01T10:49:40.361Z</v>
+        <v>2026-08-08T07:13:20.107Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -11431,7 +11431,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-01T10:49:40.376Z</v>
+        <v>2026-08-08T07:13:20.122Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -11451,7 +11451,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-01T10:49:40.392Z</v>
+        <v>2026-08-08T07:13:20.138Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -11468,10 +11468,10 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-01T10:49:40.409Z</v>
+        <v>2026-08-08T07:13:20.153Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -11488,10 +11488,10 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-01T10:49:40.423Z</v>
+        <v>2026-08-08T07:13:20.169Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -11511,7 +11511,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-01T10:49:40.440Z</v>
+        <v>2026-08-08T07:13:20.185Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -11531,7 +11531,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-01T10:49:40.455Z</v>
+        <v>2026-08-08T07:13:20.200Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -11548,10 +11548,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-01T10:49:40.470Z</v>
+        <v>2026-08-08T07:13:20.216Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -11568,10 +11568,10 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-01T10:49:40.486Z</v>
+        <v>2026-08-08T07:13:20.231Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -11591,7 +11591,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-01T10:49:40.502Z</v>
+        <v>2026-08-08T07:13:20.247Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -11611,7 +11611,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-01T10:49:40.518Z</v>
+        <v>2026-08-08T07:13:20.264Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -11631,7 +11631,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-01T10:49:40.533Z</v>
+        <v>2026-08-08T07:13:20.279Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -11651,7 +11651,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-01T10:49:40.548Z</v>
+        <v>2026-08-08T07:13:20.294Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -11668,10 +11668,10 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-01T10:49:40.563Z</v>
+        <v>2026-08-08T07:13:20.312Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -11691,7 +11691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-01T10:49:40.578Z</v>
+        <v>2026-08-08T07:13:20.326Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -11711,7 +11711,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-01T10:49:40.594Z</v>
+        <v>2026-08-08T07:13:20.342Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -11728,10 +11728,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-01T10:49:40.609Z</v>
+        <v>2026-08-08T07:13:20.358Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -11748,10 +11748,10 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-01T10:49:40.626Z</v>
+        <v>2026-08-08T07:13:20.373Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -11768,10 +11768,10 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-01T10:49:40.641Z</v>
+        <v>2026-08-08T07:13:20.389Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -11791,7 +11791,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-01T10:49:40.657Z</v>
+        <v>2026-08-08T07:13:20.404Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -11808,10 +11808,10 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-01T10:49:40.672Z</v>
+        <v>2026-08-08T07:13:20.420Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -11831,7 +11831,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-01T10:49:40.688Z</v>
+        <v>2026-08-08T07:13:20.435Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -11851,7 +11851,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-01T10:49:40.703Z</v>
+        <v>2026-08-08T07:13:20.450Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -11868,10 +11868,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-01T10:49:40.718Z</v>
+        <v>2026-08-08T07:13:20.466Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -11891,7 +11891,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-01T10:49:40.734Z</v>
+        <v>2026-08-08T07:13:20.482Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -11908,10 +11908,10 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-01T10:49:40.749Z</v>
+        <v>2026-08-08T07:13:20.498Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -11928,10 +11928,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-01T10:49:40.765Z</v>
+        <v>2026-08-08T07:13:20.512Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -11951,7 +11951,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-01T10:49:40.781Z</v>
+        <v>2026-08-08T07:13:20.529Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -11971,7 +11971,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-01T10:49:40.796Z</v>
+        <v>2026-08-08T07:13:20.543Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -11991,7 +11991,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-01T10:49:40.812Z</v>
+        <v>2026-08-08T07:13:20.559Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -12008,10 +12008,10 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-01T10:49:40.828Z</v>
+        <v>2026-08-08T07:13:20.574Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -12031,7 +12031,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-01T10:49:40.843Z</v>
+        <v>2026-08-08T07:13:20.589Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -12048,10 +12048,10 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-01T10:49:40.858Z</v>
+        <v>2026-08-08T07:13:20.605Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -12071,7 +12071,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-01T10:49:40.874Z</v>
+        <v>2026-08-08T07:13:20.621Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -12091,7 +12091,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-01T10:49:40.889Z</v>
+        <v>2026-08-08T07:13:20.636Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -12111,7 +12111,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-01T10:49:40.904Z</v>
+        <v>2026-08-08T07:13:20.651Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -12131,7 +12131,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-01T10:49:40.921Z</v>
+        <v>2026-08-08T07:13:20.667Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -12148,10 +12148,10 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-01T10:49:40.936Z</v>
+        <v>2026-08-08T07:13:20.683Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -12171,7 +12171,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-01T10:49:40.952Z</v>
+        <v>2026-08-08T07:13:20.699Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -12191,7 +12191,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-01T10:49:40.967Z</v>
+        <v>2026-08-08T07:13:20.714Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -12208,10 +12208,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-01T10:49:40.983Z</v>
+        <v>2026-08-08T07:13:20.729Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -12228,10 +12228,10 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-01T10:49:40.998Z</v>
+        <v>2026-08-08T07:13:20.745Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -12251,7 +12251,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-01T10:49:41.013Z</v>
+        <v>2026-08-08T07:13:20.760Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -12271,7 +12271,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-01T10:49:41.029Z</v>
+        <v>2026-08-08T07:13:20.776Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -12291,7 +12291,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-01T10:49:41.044Z</v>
+        <v>2026-08-08T07:13:20.791Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -12311,7 +12311,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-01T10:49:41.060Z</v>
+        <v>2026-08-08T07:13:20.808Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -12328,10 +12328,10 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-01T10:49:41.075Z</v>
+        <v>2026-08-08T07:13:20.824Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -12351,7 +12351,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-01T10:49:41.091Z</v>
+        <v>2026-08-08T07:13:20.840Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -12371,7 +12371,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-01T10:49:41.106Z</v>
+        <v>2026-08-08T07:13:20.855Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -12391,7 +12391,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-01T10:49:41.122Z</v>
+        <v>2026-08-08T07:13:20.871Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -12408,10 +12408,10 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-01T10:49:41.138Z</v>
+        <v>2026-08-08T07:13:20.886Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -12431,7 +12431,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-01T10:49:41.154Z</v>
+        <v>2026-08-08T07:13:20.903Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -12448,10 +12448,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-01T10:49:41.170Z</v>
+        <v>2026-08-08T07:13:20.918Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -12471,7 +12471,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-01T10:49:41.185Z</v>
+        <v>2026-08-08T07:13:20.933Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -12488,10 +12488,10 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-01T10:49:41.201Z</v>
+        <v>2026-08-08T07:13:20.949Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -12511,7 +12511,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-01T10:49:41.217Z</v>
+        <v>2026-08-08T07:13:20.965Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -12528,10 +12528,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-01T10:49:41.232Z</v>
+        <v>2026-08-08T07:13:20.981Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -12548,10 +12548,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-01T10:49:41.248Z</v>
+        <v>2026-08-08T07:13:20.996Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -12568,10 +12568,10 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-01T10:49:41.264Z</v>
+        <v>2026-08-08T07:13:21.011Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -12588,10 +12588,10 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-01T10:49:41.280Z</v>
+        <v>2026-08-08T07:13:21.027Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -12608,10 +12608,10 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-01T10:49:41.295Z</v>
+        <v>2026-08-08T07:13:21.043Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -12631,7 +12631,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-01T10:49:41.310Z</v>
+        <v>2026-08-08T07:13:21.058Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -12651,7 +12651,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-01T10:49:41.326Z</v>
+        <v>2026-08-08T07:13:21.075Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -12671,7 +12671,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-01T10:49:41.341Z</v>
+        <v>2026-08-08T07:13:21.090Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -12691,7 +12691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-01T10:49:41.356Z</v>
+        <v>2026-08-08T07:13:21.105Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -12711,7 +12711,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-01T10:49:41.372Z</v>
+        <v>2026-08-08T07:13:21.120Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -12731,7 +12731,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-01T10:49:41.388Z</v>
+        <v>2026-08-08T07:13:21.136Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -12751,7 +12751,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-01T10:49:41.403Z</v>
+        <v>2026-08-08T07:13:21.151Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -12771,7 +12771,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-01T10:49:41.419Z</v>
+        <v>2026-08-08T07:13:21.167Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -12788,10 +12788,10 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-01T10:49:41.435Z</v>
+        <v>2026-08-08T07:13:21.182Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -12811,7 +12811,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-01T10:49:41.451Z</v>
+        <v>2026-08-08T07:13:21.198Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -12831,7 +12831,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-01T10:49:41.467Z</v>
+        <v>2026-08-08T07:13:21.215Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -12851,7 +12851,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-01T10:49:41.483Z</v>
+        <v>2026-08-08T07:13:21.233Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -12868,10 +12868,10 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-01T10:49:41.499Z</v>
+        <v>2026-08-08T07:13:21.248Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -12891,7 +12891,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-01T10:49:41.513Z</v>
+        <v>2026-08-08T07:13:21.263Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -12908,10 +12908,10 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-01T10:49:41.529Z</v>
+        <v>2026-08-08T07:13:21.278Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -12931,7 +12931,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-01T10:49:41.545Z</v>
+        <v>2026-08-08T07:13:21.294Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -12951,7 +12951,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-01T10:49:41.560Z</v>
+        <v>2026-08-08T07:13:21.309Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -12968,10 +12968,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-01T10:49:41.575Z</v>
+        <v>2026-08-08T07:13:21.325Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -12991,7 +12991,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-01T10:49:41.592Z</v>
+        <v>2026-08-08T07:13:21.341Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -13008,10 +13008,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-01T10:49:41.607Z</v>
+        <v>2026-08-08T07:13:21.357Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -13031,7 +13031,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-01T10:49:41.623Z</v>
+        <v>2026-08-08T07:13:21.373Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -13051,7 +13051,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-01T10:49:41.639Z</v>
+        <v>2026-08-08T07:13:21.389Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -13071,7 +13071,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-01T10:49:41.654Z</v>
+        <v>2026-08-08T07:13:21.404Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -13091,7 +13091,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-01T10:49:41.670Z</v>
+        <v>2026-08-08T07:13:21.420Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -13108,10 +13108,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-01T10:49:41.685Z</v>
+        <v>2026-08-08T07:13:21.436Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -13131,7 +13131,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-01T10:49:41.701Z</v>
+        <v>2026-08-08T07:13:21.452Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -13148,10 +13148,10 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-01T10:49:41.717Z</v>
+        <v>2026-08-08T07:13:21.467Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -13168,10 +13168,10 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-01T10:49:41.733Z</v>
+        <v>2026-08-08T07:13:21.482Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -13191,7 +13191,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-01T10:49:41.749Z</v>
+        <v>2026-08-08T07:13:21.498Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -13208,10 +13208,10 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-01T10:49:41.765Z</v>
+        <v>2026-08-08T07:13:21.513Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -13231,7 +13231,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-01T10:49:41.779Z</v>
+        <v>2026-08-08T07:13:21.528Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -13248,10 +13248,10 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-01T10:49:41.794Z</v>
+        <v>2026-08-08T07:13:21.544Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -13271,7 +13271,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-01T10:49:41.809Z</v>
+        <v>2026-08-08T07:13:21.559Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -13291,7 +13291,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-01T10:49:41.825Z</v>
+        <v>2026-08-08T07:13:21.574Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -13311,7 +13311,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-01T10:49:41.841Z</v>
+        <v>2026-08-08T07:13:21.590Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -13331,7 +13331,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-01T10:49:41.855Z</v>
+        <v>2026-08-08T07:13:21.605Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -13348,10 +13348,10 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-01T10:49:41.872Z</v>
+        <v>2026-08-08T07:13:21.620Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -13371,7 +13371,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-01T10:49:41.888Z</v>
+        <v>2026-08-08T07:13:21.636Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -13388,10 +13388,10 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-01T10:49:41.903Z</v>
+        <v>2026-08-08T07:13:21.652Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -13411,7 +13411,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-01T10:49:41.919Z</v>
+        <v>2026-08-08T07:13:21.668Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -13431,7 +13431,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-01T10:49:41.935Z</v>
+        <v>2026-08-08T07:13:21.685Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -13451,7 +13451,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-01T10:49:41.950Z</v>
+        <v>2026-08-08T07:13:21.700Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -13471,7 +13471,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-01T10:49:41.966Z</v>
+        <v>2026-08-08T07:13:21.716Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -13491,7 +13491,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-01T10:49:41.982Z</v>
+        <v>2026-08-08T07:13:21.732Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -13508,10 +13508,10 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-01T10:49:41.997Z</v>
+        <v>2026-08-08T07:13:21.748Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -13531,7 +13531,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-01T10:49:42.012Z</v>
+        <v>2026-08-08T07:13:21.763Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -13548,10 +13548,10 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-01T10:49:42.028Z</v>
+        <v>2026-08-08T07:13:21.778Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -13571,7 +13571,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-01T10:49:42.044Z</v>
+        <v>2026-08-08T07:13:21.795Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -13591,7 +13591,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-01T10:49:42.059Z</v>
+        <v>2026-08-08T07:13:21.810Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -13608,10 +13608,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-01T10:49:42.075Z</v>
+        <v>2026-08-08T07:13:21.825Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -13628,10 +13628,10 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-01T10:49:42.090Z</v>
+        <v>2026-08-08T07:13:21.842Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -13651,7 +13651,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-01T10:49:42.105Z</v>
+        <v>2026-08-08T07:13:21.856Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -13671,7 +13671,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-01T10:49:42.121Z</v>
+        <v>2026-08-08T07:13:21.873Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -13688,10 +13688,10 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-01T10:49:42.136Z</v>
+        <v>2026-08-08T07:13:21.889Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -13708,10 +13708,10 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-01T10:49:42.152Z</v>
+        <v>2026-08-08T07:13:21.905Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -13731,7 +13731,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-01T10:49:42.167Z</v>
+        <v>2026-08-08T07:13:21.920Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -13751,7 +13751,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-01T10:49:42.183Z</v>
+        <v>2026-08-08T07:13:21.936Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -13771,7 +13771,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-01T10:49:42.199Z</v>
+        <v>2026-08-08T07:13:21.952Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -13791,7 +13791,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-01T10:49:42.214Z</v>
+        <v>2026-08-08T07:13:21.967Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -13811,7 +13811,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-01T10:49:42.230Z</v>
+        <v>2026-08-08T07:13:21.984Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -13828,10 +13828,10 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-01T10:49:42.246Z</v>
+        <v>2026-08-08T07:13:21.999Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -13848,10 +13848,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-01T10:49:42.262Z</v>
+        <v>2026-08-08T07:13:22.014Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -13871,7 +13871,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-01T10:49:42.277Z</v>
+        <v>2026-08-08T07:13:22.029Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -13891,7 +13891,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-01T10:49:42.293Z</v>
+        <v>2026-08-08T07:13:22.045Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -13911,7 +13911,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-01T10:49:42.308Z</v>
+        <v>2026-08-08T07:13:22.061Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -13931,7 +13931,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-01T10:49:42.324Z</v>
+        <v>2026-08-08T07:13:22.077Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -13951,7 +13951,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-01T10:49:42.339Z</v>
+        <v>2026-08-08T07:13:22.092Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -13971,7 +13971,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-01T10:49:42.355Z</v>
+        <v>2026-08-08T07:13:22.108Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -13988,10 +13988,10 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-01T10:49:42.372Z</v>
+        <v>2026-08-08T07:13:22.123Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -14011,7 +14011,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-01T10:49:42.386Z</v>
+        <v>2026-08-08T07:13:22.138Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -14031,7 +14031,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-01T10:49:42.402Z</v>
+        <v>2026-08-08T07:13:22.154Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -14051,7 +14051,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-01T10:49:42.417Z</v>
+        <v>2026-08-08T07:13:22.169Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -14071,7 +14071,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-01T10:49:42.433Z</v>
+        <v>2026-08-08T07:13:22.185Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -14088,10 +14088,10 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-01T10:49:42.449Z</v>
+        <v>2026-08-08T07:13:22.200Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -14111,7 +14111,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-01T10:49:42.464Z</v>
+        <v>2026-08-08T07:13:22.216Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -14128,10 +14128,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-01T10:49:42.480Z</v>
+        <v>2026-08-08T07:13:22.231Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -14151,7 +14151,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-01T10:49:42.495Z</v>
+        <v>2026-08-08T07:13:22.247Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -14168,10 +14168,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-01T10:49:42.511Z</v>
+        <v>2026-08-08T07:13:22.262Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -14188,10 +14188,10 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-01T10:49:42.525Z</v>
+        <v>2026-08-08T07:13:22.278Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -14211,7 +14211,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-01T10:49:42.540Z</v>
+        <v>2026-08-08T07:13:22.294Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -14231,7 +14231,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-01T10:49:42.555Z</v>
+        <v>2026-08-08T07:13:22.309Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -14248,10 +14248,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-01T10:49:42.571Z</v>
+        <v>2026-08-08T07:13:22.325Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -14268,10 +14268,10 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-01T10:49:42.587Z</v>
+        <v>2026-08-08T07:13:22.341Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -14288,10 +14288,10 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-01T10:49:42.603Z</v>
+        <v>2026-08-08T07:13:22.356Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -14311,7 +14311,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-01T10:49:42.618Z</v>
+        <v>2026-08-08T07:13:22.371Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -14328,10 +14328,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-01T10:49:42.633Z</v>
+        <v>2026-08-08T07:13:22.387Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -14351,7 +14351,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-01T10:49:42.649Z</v>
+        <v>2026-08-08T07:13:22.403Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -14368,10 +14368,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-01T10:49:42.664Z</v>
+        <v>2026-08-08T07:13:22.419Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -14391,7 +14391,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-01T10:49:42.680Z</v>
+        <v>2026-08-08T07:13:22.435Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -14408,10 +14408,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-01T10:49:42.696Z</v>
+        <v>2026-08-08T07:13:22.450Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -14428,10 +14428,10 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-01T10:49:42.711Z</v>
+        <v>2026-08-08T07:13:22.466Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -14451,7 +14451,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-01T10:49:42.727Z</v>
+        <v>2026-08-08T07:13:22.482Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -14471,7 +14471,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-01T10:49:42.742Z</v>
+        <v>2026-08-08T07:13:22.497Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -14488,10 +14488,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-01T10:49:42.758Z</v>
+        <v>2026-08-08T07:13:22.513Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -14511,7 +14511,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-01T10:49:42.774Z</v>
+        <v>2026-08-08T07:13:22.528Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -14528,10 +14528,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-01T10:49:42.789Z</v>
+        <v>2026-08-08T07:13:22.544Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -14551,7 +14551,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-01T10:49:42.805Z</v>
+        <v>2026-08-08T07:13:22.560Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -14571,7 +14571,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-01T10:49:42.820Z</v>
+        <v>2026-08-08T07:13:22.575Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -14588,10 +14588,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-01T10:49:42.835Z</v>
+        <v>2026-08-08T07:13:22.591Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -14608,10 +14608,10 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-01T10:49:42.851Z</v>
+        <v>2026-08-08T07:13:22.606Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -14631,7 +14631,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-01T10:49:42.867Z</v>
+        <v>2026-08-08T07:13:22.622Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -14648,10 +14648,10 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-01T10:49:42.883Z</v>
+        <v>2026-08-08T07:13:22.637Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -14668,10 +14668,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-01T10:49:42.898Z</v>
+        <v>2026-08-08T07:13:22.654Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -14691,7 +14691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-01T10:49:42.913Z</v>
+        <v>2026-08-08T07:13:22.669Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -14711,7 +14711,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-01T10:49:42.928Z</v>
+        <v>2026-08-08T07:13:22.684Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -14731,7 +14731,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-01T10:49:42.944Z</v>
+        <v>2026-08-08T07:13:22.700Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -14748,10 +14748,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-01T10:49:42.960Z</v>
+        <v>2026-08-08T07:13:22.715Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -14768,10 +14768,10 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-01T10:49:42.975Z</v>
+        <v>2026-08-08T07:13:22.732Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -14788,10 +14788,10 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-01T10:49:42.991Z</v>
+        <v>2026-08-08T07:13:22.747Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -14811,7 +14811,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-01T10:49:43.007Z</v>
+        <v>2026-08-08T07:13:22.763Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -14828,10 +14828,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-01T10:49:43.023Z</v>
+        <v>2026-08-08T07:13:22.778Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -14851,7 +14851,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-01T10:49:43.039Z</v>
+        <v>2026-08-08T07:13:22.794Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -14871,7 +14871,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-01T10:49:43.055Z</v>
+        <v>2026-08-08T07:13:22.809Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -14888,10 +14888,10 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-01T10:49:43.070Z</v>
+        <v>2026-08-08T07:13:22.825Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -14908,10 +14908,10 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-01T10:49:43.086Z</v>
+        <v>2026-08-08T07:13:22.840Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -14931,7 +14931,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-01T10:49:43.101Z</v>
+        <v>2026-08-08T07:13:22.855Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -14951,7 +14951,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-01T10:49:43.117Z</v>
+        <v>2026-08-08T07:13:22.872Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -14968,10 +14968,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-01T10:49:43.134Z</v>
+        <v>2026-08-08T07:13:22.887Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -14988,10 +14988,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-01T10:49:43.150Z</v>
+        <v>2026-08-08T07:13:22.903Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -15008,10 +15008,10 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-01T10:49:43.164Z</v>
+        <v>2026-08-08T07:13:22.919Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -15031,7 +15031,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-01T10:49:43.180Z</v>
+        <v>2026-08-08T07:13:22.935Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -15048,10 +15048,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-01T10:49:43.196Z</v>
+        <v>2026-08-08T07:13:22.950Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -15068,10 +15068,10 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-01T10:49:43.211Z</v>
+        <v>2026-08-08T07:13:22.966Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -15091,7 +15091,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-01T10:49:43.226Z</v>
+        <v>2026-08-08T07:13:22.981Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -15108,10 +15108,10 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-01T10:49:43.242Z</v>
+        <v>2026-08-08T07:13:22.997Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -15128,10 +15128,10 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-01T10:49:43.257Z</v>
+        <v>2026-08-08T07:13:23.013Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -15148,10 +15148,10 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-01T10:49:43.273Z</v>
+        <v>2026-08-08T07:13:23.028Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -15168,10 +15168,10 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-01T10:49:43.289Z</v>
+        <v>2026-08-08T07:13:23.044Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -15191,7 +15191,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-01T10:49:43.305Z</v>
+        <v>2026-08-08T07:13:23.060Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -15211,7 +15211,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-01T10:49:43.320Z</v>
+        <v>2026-08-08T07:13:23.075Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -15228,10 +15228,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-01T10:49:43.336Z</v>
+        <v>2026-08-08T07:13:23.090Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -15251,7 +15251,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-01T10:49:43.352Z</v>
+        <v>2026-08-08T07:13:23.106Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -15268,10 +15268,10 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-01T10:49:43.368Z</v>
+        <v>2026-08-08T07:13:23.121Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -15291,7 +15291,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-01T10:49:43.383Z</v>
+        <v>2026-08-08T07:13:23.136Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -15308,10 +15308,10 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-01T10:49:43.399Z</v>
+        <v>2026-08-08T07:13:23.152Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -15328,10 +15328,10 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-01T10:49:43.414Z</v>
+        <v>2026-08-08T07:13:23.168Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -15348,10 +15348,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-01T10:49:43.430Z</v>
+        <v>2026-08-08T07:13:23.183Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -15371,7 +15371,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-01T10:49:43.446Z</v>
+        <v>2026-08-08T07:13:23.199Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -15388,10 +15388,10 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-01T10:49:43.462Z</v>
+        <v>2026-08-08T07:13:23.214Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -15408,10 +15408,10 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-01T10:49:43.477Z</v>
+        <v>2026-08-08T07:13:23.230Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -15428,10 +15428,10 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-01T10:49:43.492Z</v>
+        <v>2026-08-08T07:13:23.247Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -15451,7 +15451,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-01T10:49:43.508Z</v>
+        <v>2026-08-08T07:13:23.265Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -15471,7 +15471,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-01T10:49:43.523Z</v>
+        <v>2026-08-08T07:13:23.278Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -15488,10 +15488,10 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-01T10:49:43.539Z</v>
+        <v>2026-08-08T07:13:23.293Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -15508,10 +15508,10 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-01T10:49:43.555Z</v>
+        <v>2026-08-08T07:13:23.308Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -15531,7 +15531,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-01T10:49:43.571Z</v>
+        <v>2026-08-08T07:13:23.324Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -15551,7 +15551,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-01T10:49:43.587Z</v>
+        <v>2026-08-08T07:13:23.343Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -15571,7 +15571,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-01T10:49:43.602Z</v>
+        <v>2026-08-08T07:13:23.356Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -15588,10 +15588,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-01T10:49:43.618Z</v>
+        <v>2026-08-08T07:13:23.371Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -15608,10 +15608,10 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-01T10:49:43.633Z</v>
+        <v>2026-08-08T07:13:23.387Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -15628,10 +15628,10 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-01T10:49:43.649Z</v>
+        <v>2026-08-08T07:13:23.401Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -15651,7 +15651,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-01T10:49:43.665Z</v>
+        <v>2026-08-08T07:13:23.418Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -15671,7 +15671,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-01T10:49:43.681Z</v>
+        <v>2026-08-08T07:13:23.434Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -15691,7 +15691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-01T10:49:43.696Z</v>
+        <v>2026-08-08T07:13:23.449Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -15711,7 +15711,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-01T10:49:43.712Z</v>
+        <v>2026-08-08T07:13:23.465Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -15728,10 +15728,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-01T10:49:43.728Z</v>
+        <v>2026-08-08T07:13:23.479Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -15748,10 +15748,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-01T10:49:43.743Z</v>
+        <v>2026-08-08T07:13:23.495Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -15771,7 +15771,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-01T10:49:43.759Z</v>
+        <v>2026-08-08T07:13:23.511Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -15788,10 +15788,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-01T10:49:43.774Z</v>
+        <v>2026-08-08T07:13:23.527Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -15811,7 +15811,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-01T10:49:43.790Z</v>
+        <v>2026-08-08T07:13:23.543Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -15828,10 +15828,10 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-01T10:49:43.806Z</v>
+        <v>2026-08-08T07:13:23.558Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -15851,7 +15851,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-01T10:49:43.821Z</v>
+        <v>2026-08-08T07:13:23.573Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -15871,7 +15871,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-01T10:49:43.837Z</v>
+        <v>2026-08-08T07:13:23.589Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -15888,10 +15888,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-01T10:49:43.852Z</v>
+        <v>2026-08-08T07:13:23.605Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -15911,7 +15911,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-01T10:49:43.868Z</v>
+        <v>2026-08-08T07:13:23.621Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -15931,7 +15931,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-01T10:49:43.884Z</v>
+        <v>2026-08-08T07:13:23.637Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -15951,7 +15951,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-01T10:49:43.899Z</v>
+        <v>2026-08-08T07:13:23.652Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -15968,10 +15968,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-01T10:49:43.915Z</v>
+        <v>2026-08-08T07:13:23.667Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -15988,10 +15988,10 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-01T10:49:43.931Z</v>
+        <v>2026-08-08T07:13:23.682Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -16011,7 +16011,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-01T10:49:43.947Z</v>
+        <v>2026-08-08T07:13:23.698Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -16028,10 +16028,10 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-01T10:49:43.962Z</v>
+        <v>2026-08-08T07:13:23.714Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -16051,7 +16051,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-01T10:49:43.977Z</v>
+        <v>2026-08-08T07:13:23.729Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -16071,7 +16071,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-01T10:49:43.993Z</v>
+        <v>2026-08-08T07:13:23.746Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -16088,10 +16088,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-01T10:49:44.008Z</v>
+        <v>2026-08-08T07:13:23.763Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -16111,7 +16111,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-01T10:49:44.023Z</v>
+        <v>2026-08-08T07:13:23.777Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -16131,7 +16131,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-01T10:49:44.039Z</v>
+        <v>2026-08-08T07:13:23.793Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -16148,10 +16148,10 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-01T10:49:44.054Z</v>
+        <v>2026-08-08T07:13:23.809Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -16168,10 +16168,10 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-01T10:49:44.070Z</v>
+        <v>2026-08-08T07:13:23.824Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -16191,7 +16191,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-01T10:49:44.085Z</v>
+        <v>2026-08-08T07:13:23.839Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -16208,10 +16208,10 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-01T10:49:44.101Z</v>
+        <v>2026-08-08T07:13:23.854Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -16231,7 +16231,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-01T10:49:44.116Z</v>
+        <v>2026-08-08T07:13:23.870Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -16251,7 +16251,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-01T10:49:44.132Z</v>
+        <v>2026-08-08T07:13:23.886Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -16271,7 +16271,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-01T10:49:44.147Z</v>
+        <v>2026-08-08T07:13:23.900Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -16288,10 +16288,10 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-01T10:49:44.163Z</v>
+        <v>2026-08-08T07:13:23.915Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -16308,10 +16308,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-01T10:49:44.178Z</v>
+        <v>2026-08-08T07:13:23.932Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -16328,10 +16328,10 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-01T10:49:44.194Z</v>
+        <v>2026-08-08T07:13:23.947Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -16348,10 +16348,10 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-01T10:49:44.210Z</v>
+        <v>2026-08-08T07:13:23.963Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -16368,10 +16368,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-01T10:49:44.225Z</v>
+        <v>2026-08-08T07:13:23.979Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -16388,10 +16388,10 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-01T10:49:44.240Z</v>
+        <v>2026-08-08T07:13:23.995Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -16408,10 +16408,10 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-01T10:49:44.255Z</v>
+        <v>2026-08-08T07:13:24.011Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -16428,10 +16428,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-01T10:49:44.271Z</v>
+        <v>2026-08-08T07:13:24.026Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -16448,10 +16448,10 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-01T10:49:44.286Z</v>
+        <v>2026-08-08T07:13:24.043Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -16468,10 +16468,10 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-01T10:49:44.302Z</v>
+        <v>2026-08-08T07:13:24.059Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -16488,10 +16488,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-01T10:49:44.318Z</v>
+        <v>2026-08-08T07:13:24.073Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -16511,7 +16511,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-01T10:49:44.334Z</v>
+        <v>2026-08-08T07:13:24.089Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -16531,7 +16531,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-01T10:49:44.348Z</v>
+        <v>2026-08-08T07:13:24.104Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -16548,10 +16548,10 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-01T10:49:44.363Z</v>
+        <v>2026-08-08T07:13:24.120Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -16571,7 +16571,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-01T10:49:44.378Z</v>
+        <v>2026-08-08T07:13:24.135Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -16591,7 +16591,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-01T10:49:44.394Z</v>
+        <v>2026-08-08T07:13:24.151Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -16611,7 +16611,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-01T10:49:44.409Z</v>
+        <v>2026-08-08T07:13:24.166Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -16631,7 +16631,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-01T10:49:44.425Z</v>
+        <v>2026-08-08T07:13:24.182Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -16651,7 +16651,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-01T10:49:44.440Z</v>
+        <v>2026-08-08T07:13:24.197Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -16671,7 +16671,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-01T10:49:44.456Z</v>
+        <v>2026-08-08T07:13:24.214Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -16691,7 +16691,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-01T10:49:44.471Z</v>
+        <v>2026-08-08T07:13:24.229Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>

--- a/reports/Total_Test_Cases_Report.xlsx
+++ b/reports/Total_Test_Cases_Report.xlsx
@@ -509,13 +509,13 @@
         <v>400</v>
       </c>
       <c r="C8">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>50.00%</v>
+        <v>100.00%</v>
       </c>
       <c r="F8" t="str">
         <v>PASS</v>
@@ -571,7 +571,7 @@
         <v>Average Latency (ms)</v>
       </c>
       <c r="B16">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="17">
@@ -600,7 +600,7 @@
         <v>Report Consolidated Time</v>
       </c>
       <c r="B21" t="str">
-        <v>9/8/2026, 11:49:46 pm</v>
+        <v>11/8/2026, 9:25:08 am</v>
       </c>
     </row>
     <row r="22">
@@ -669,10 +669,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>4.33 sec</v>
+        <v>2.50 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
@@ -693,7 +693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -713,7 +713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -733,7 +733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -753,7 +753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -773,7 +773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -793,7 +793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -813,7 +813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -833,7 +833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -853,7 +853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -873,7 +873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -893,7 +893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -913,7 +913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -933,7 +933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -953,7 +953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -973,7 +973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -993,7 +993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -1013,7 +1013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -1033,7 +1033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -1053,7 +1053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -1073,7 +1073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -1093,7 +1093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -1113,7 +1113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -1133,7 +1133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -1153,7 +1153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -1173,7 +1173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -1193,7 +1193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -1213,7 +1213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -1233,7 +1233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1253,7 +1253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1273,7 +1273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1293,7 +1293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1313,7 +1313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1333,7 +1333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1353,7 +1353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1373,7 +1373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1393,7 +1393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1413,7 +1413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1433,7 +1433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1453,7 +1453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1473,7 +1473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1493,7 +1493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1513,7 +1513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1533,7 +1533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1553,7 +1553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1573,7 +1573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1593,7 +1593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1613,7 +1613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1633,7 +1633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1653,7 +1653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1673,7 +1673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1693,7 +1693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1713,7 +1713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1733,7 +1733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1753,7 +1753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1773,7 +1773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1793,7 +1793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1813,7 +1813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1833,7 +1833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1853,7 +1853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1873,7 +1873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1893,7 +1893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1913,7 +1913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1933,7 +1933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1953,7 +1953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1973,7 +1973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1993,7 +1993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -2013,7 +2013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -2033,7 +2033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -2053,7 +2053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -2073,7 +2073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -2093,7 +2093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -2113,7 +2113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -2133,7 +2133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -2153,7 +2153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -2173,7 +2173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -2193,7 +2193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -2213,7 +2213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -2233,7 +2233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2253,7 +2253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2273,7 +2273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2293,7 +2293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2313,7 +2313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2333,7 +2333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2353,7 +2353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2373,7 +2373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2393,7 +2393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2413,7 +2413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2433,7 +2433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2453,7 +2453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2473,7 +2473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2493,7 +2493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2513,7 +2513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2533,7 +2533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2553,7 +2553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2573,7 +2573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2593,7 +2593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2613,7 +2613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2633,7 +2633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2653,7 +2653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2673,7 +2673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2693,7 +2693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2713,7 +2713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2733,7 +2733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2753,7 +2753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2773,7 +2773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2793,7 +2793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2813,7 +2813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2833,7 +2833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2853,7 +2853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2873,7 +2873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2893,7 +2893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2913,7 +2913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2933,7 +2933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2953,7 +2953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2973,7 +2973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2993,7 +2993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -3013,7 +3013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -3033,7 +3033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -3053,7 +3053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -3073,7 +3073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -3093,7 +3093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -3113,7 +3113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -3133,7 +3133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -3153,7 +3153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -3173,7 +3173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -3193,7 +3193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -3213,7 +3213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -3233,7 +3233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3253,7 +3253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3273,7 +3273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3293,7 +3293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3313,7 +3313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3333,7 +3333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3353,7 +3353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3373,7 +3373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3393,7 +3393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3413,7 +3413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3433,7 +3433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3453,7 +3453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3473,7 +3473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3493,7 +3493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3513,7 +3513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3533,7 +3533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3553,7 +3553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3573,7 +3573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3593,7 +3593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3613,7 +3613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3633,7 +3633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3653,7 +3653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3673,7 +3673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3693,7 +3693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3713,7 +3713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3733,7 +3733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3753,7 +3753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3773,7 +3773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3793,7 +3793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3813,7 +3813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3833,7 +3833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3853,7 +3853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3873,7 +3873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3893,7 +3893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3913,7 +3913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3933,7 +3933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3953,7 +3953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3973,7 +3973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3993,7 +3993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -4013,7 +4013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -4033,7 +4033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -4053,7 +4053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -4073,7 +4073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -4093,7 +4093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -4113,7 +4113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -4133,7 +4133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -4153,7 +4153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -4173,7 +4173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -4193,7 +4193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -4213,7 +4213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -4233,7 +4233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4253,7 +4253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4273,7 +4273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4293,7 +4293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4313,7 +4313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4333,7 +4333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4353,7 +4353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4373,7 +4373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4393,7 +4393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4413,7 +4413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4433,7 +4433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4453,7 +4453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4473,7 +4473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4493,7 +4493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4513,7 +4513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4533,7 +4533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4553,7 +4553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4573,7 +4573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4593,7 +4593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4613,7 +4613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4633,7 +4633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4653,7 +4653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4673,7 +4673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4693,7 +4693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4713,7 +4713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4733,7 +4733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4753,7 +4753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4773,7 +4773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4793,7 +4793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4813,7 +4813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4833,7 +4833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4853,7 +4853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4873,7 +4873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4893,7 +4893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4913,7 +4913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4933,7 +4933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4953,7 +4953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4973,7 +4973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4993,7 +4993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -5013,7 +5013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -5033,7 +5033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -5053,7 +5053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -5073,7 +5073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -5093,7 +5093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -5113,7 +5113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -5133,7 +5133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -5153,7 +5153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -5173,7 +5173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -5193,7 +5193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -5213,7 +5213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -5233,7 +5233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5253,7 +5253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5273,7 +5273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5293,7 +5293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5313,7 +5313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5333,7 +5333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5353,7 +5353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5373,7 +5373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5393,7 +5393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5413,7 +5413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5433,7 +5433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5453,7 +5453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5473,7 +5473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5493,7 +5493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5513,7 +5513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5533,7 +5533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5553,7 +5553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5573,7 +5573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5593,7 +5593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5613,7 +5613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5633,7 +5633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5653,7 +5653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5673,7 +5673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5693,7 +5693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5713,7 +5713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5733,7 +5733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5753,7 +5753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5773,7 +5773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5793,7 +5793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5813,7 +5813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5833,7 +5833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5853,7 +5853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5873,7 +5873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5893,7 +5893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5913,7 +5913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5933,7 +5933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5953,7 +5953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5973,7 +5973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5993,7 +5993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -6013,7 +6013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -6033,7 +6033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -6053,7 +6053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -6073,7 +6073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -6093,7 +6093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -6113,7 +6113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -6133,7 +6133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -6153,7 +6153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -6173,7 +6173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -6193,7 +6193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -6213,7 +6213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -6233,7 +6233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6253,7 +6253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6273,7 +6273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6293,7 +6293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6313,7 +6313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6333,7 +6333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6353,7 +6353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6373,7 +6373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6393,7 +6393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6413,7 +6413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6433,7 +6433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6453,7 +6453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6473,7 +6473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6493,7 +6493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6513,7 +6513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6533,7 +6533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6553,7 +6553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6573,7 +6573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6593,7 +6593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6613,7 +6613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6633,7 +6633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6653,7 +6653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6673,7 +6673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6693,7 +6693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6713,7 +6713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6733,7 +6733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6753,7 +6753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6773,7 +6773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6793,7 +6793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6813,7 +6813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6833,7 +6833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6853,7 +6853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6873,7 +6873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6893,7 +6893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6913,7 +6913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6933,7 +6933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6953,7 +6953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6973,7 +6973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6993,7 +6993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -7013,7 +7013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -7033,7 +7033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -7053,7 +7053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -7073,7 +7073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -7093,7 +7093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -7113,7 +7113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -7133,7 +7133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -7153,7 +7153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -7173,7 +7173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -7193,7 +7193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -7213,7 +7213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -7233,7 +7233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7253,7 +7253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7273,7 +7273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7293,7 +7293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7313,7 +7313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7333,7 +7333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7353,7 +7353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7373,7 +7373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7393,7 +7393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7413,7 +7413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7433,7 +7433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7453,7 +7453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7473,7 +7473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7493,7 +7493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7513,7 +7513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7533,7 +7533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7553,7 +7553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7573,7 +7573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7593,7 +7593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7613,7 +7613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7633,7 +7633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7653,7 +7653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7673,7 +7673,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7693,7 +7693,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7713,7 +7713,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7733,7 +7733,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7753,7 +7753,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7773,7 +7773,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7793,7 +7793,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7813,7 +7813,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7833,7 +7833,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7853,7 +7853,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7873,7 +7873,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7893,7 +7893,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7913,7 +7913,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7933,7 +7933,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7953,7 +7953,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7973,7 +7973,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7993,7 +7993,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -8013,7 +8013,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -8033,7 +8033,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -8053,7 +8053,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -8073,7 +8073,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -8093,7 +8093,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -8113,7 +8113,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -8133,7 +8133,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -8153,7 +8153,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -8173,7 +8173,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -8193,7 +8193,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -8213,7 +8213,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -8233,7 +8233,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8253,7 +8253,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8273,7 +8273,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8293,7 +8293,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8313,7 +8313,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8333,7 +8333,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8353,7 +8353,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8373,7 +8373,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8393,7 +8393,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8413,7 +8413,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8433,7 +8433,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8453,7 +8453,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8473,7 +8473,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8493,7 +8493,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8513,7 +8513,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8533,7 +8533,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8553,7 +8553,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8573,7 +8573,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8593,7 +8593,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8613,7 +8613,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8633,7 +8633,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8653,7 +8653,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>
@@ -8712,7 +8712,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-09T18:19:35.426Z</v>
+        <v>2026-08-09T18:22:57.692Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -8732,7 +8732,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-09T18:19:35.432Z</v>
+        <v>2026-08-09T18:22:57.698Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -8749,10 +8749,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-09T18:19:35.446Z</v>
+        <v>2026-08-09T18:22:57.717Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -8772,7 +8772,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-09T18:19:35.462Z</v>
+        <v>2026-08-09T18:22:57.733Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -8789,10 +8789,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-09T18:19:35.477Z</v>
+        <v>2026-08-09T18:22:57.749Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -8809,10 +8809,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-09T18:19:35.492Z</v>
+        <v>2026-08-09T18:22:57.765Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -8829,10 +8829,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-09T18:19:35.508Z</v>
+        <v>2026-08-09T18:22:57.780Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -8852,7 +8852,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-09T18:19:35.524Z</v>
+        <v>2026-08-09T18:22:57.796Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -8869,10 +8869,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-09T18:19:35.539Z</v>
+        <v>2026-08-09T18:22:57.812Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -8892,7 +8892,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-09T18:19:35.554Z</v>
+        <v>2026-08-09T18:22:57.827Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -8912,7 +8912,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-09T18:19:35.570Z</v>
+        <v>2026-08-09T18:22:57.843Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -8932,7 +8932,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-09T18:19:35.586Z</v>
+        <v>2026-08-09T18:22:57.858Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -8952,7 +8952,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-09T18:19:35.602Z</v>
+        <v>2026-08-09T18:22:57.874Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -8972,7 +8972,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-09T18:19:35.617Z</v>
+        <v>2026-08-09T18:22:57.889Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -8989,10 +8989,10 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-09T18:19:35.633Z</v>
+        <v>2026-08-09T18:22:57.904Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -9012,7 +9012,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-09T18:19:35.648Z</v>
+        <v>2026-08-09T18:22:57.920Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -9032,7 +9032,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-09T18:19:35.663Z</v>
+        <v>2026-08-09T18:22:57.935Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -9052,7 +9052,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-09T18:19:35.681Z</v>
+        <v>2026-08-09T18:22:57.951Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -9072,7 +9072,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-09T18:19:35.695Z</v>
+        <v>2026-08-09T18:22:57.966Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -9089,10 +9089,10 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-09T18:19:35.710Z</v>
+        <v>2026-08-09T18:22:57.982Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -9112,7 +9112,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-09T18:19:35.726Z</v>
+        <v>2026-08-09T18:22:57.998Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -9132,7 +9132,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-09T18:19:35.741Z</v>
+        <v>2026-08-09T18:22:58.013Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -9152,7 +9152,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09T18:19:35.756Z</v>
+        <v>2026-08-09T18:22:58.029Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -9169,10 +9169,10 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-09T18:19:35.773Z</v>
+        <v>2026-08-09T18:22:58.044Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -9192,7 +9192,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-09T18:19:35.788Z</v>
+        <v>2026-08-09T18:22:58.059Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -9209,10 +9209,10 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-09T18:19:35.804Z</v>
+        <v>2026-08-09T18:22:58.074Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -9232,7 +9232,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-09T18:19:35.820Z</v>
+        <v>2026-08-09T18:22:58.091Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -9252,7 +9252,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-09T18:19:35.835Z</v>
+        <v>2026-08-09T18:22:58.106Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -9272,7 +9272,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-09T18:19:35.851Z</v>
+        <v>2026-08-09T18:22:58.122Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -9289,10 +9289,10 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-09T18:19:35.867Z</v>
+        <v>2026-08-09T18:22:58.137Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -9312,7 +9312,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-09T18:19:35.882Z</v>
+        <v>2026-08-09T18:22:58.153Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -9329,10 +9329,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-09T18:19:35.897Z</v>
+        <v>2026-08-09T18:22:58.169Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -9352,7 +9352,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-09T18:19:35.912Z</v>
+        <v>2026-08-09T18:22:58.184Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -9372,7 +9372,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-09T18:19:35.927Z</v>
+        <v>2026-08-09T18:22:58.199Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -9389,10 +9389,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-09T18:19:35.942Z</v>
+        <v>2026-08-09T18:22:58.215Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -9412,7 +9412,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-09T18:19:35.957Z</v>
+        <v>2026-08-09T18:22:58.231Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -9432,7 +9432,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-09T18:19:35.972Z</v>
+        <v>2026-08-09T18:22:58.246Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -9452,7 +9452,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-09T18:19:35.987Z</v>
+        <v>2026-08-09T18:22:58.261Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -9472,7 +9472,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-09T18:19:36.003Z</v>
+        <v>2026-08-09T18:22:58.277Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -9489,10 +9489,10 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-09T18:19:36.019Z</v>
+        <v>2026-08-09T18:22:58.293Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -9512,7 +9512,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-09T18:19:36.034Z</v>
+        <v>2026-08-09T18:22:58.309Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -9529,10 +9529,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-09T18:19:36.049Z</v>
+        <v>2026-08-09T18:22:58.325Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -9549,10 +9549,10 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-09T18:19:36.065Z</v>
+        <v>2026-08-09T18:22:58.341Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -9569,10 +9569,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-09T18:19:36.081Z</v>
+        <v>2026-08-09T18:22:58.356Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -9589,10 +9589,10 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-09T18:19:36.097Z</v>
+        <v>2026-08-09T18:22:58.371Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -9612,7 +9612,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-09T18:19:36.112Z</v>
+        <v>2026-08-09T18:22:58.386Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -9632,7 +9632,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-09T18:19:36.128Z</v>
+        <v>2026-08-09T18:22:58.402Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -9652,7 +9652,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-09T18:19:36.144Z</v>
+        <v>2026-08-09T18:22:58.419Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -9669,10 +9669,10 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-09T18:19:36.160Z</v>
+        <v>2026-08-09T18:22:58.433Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -9692,7 +9692,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-09T18:19:36.176Z</v>
+        <v>2026-08-09T18:22:58.449Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -9709,10 +9709,10 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-09T18:19:36.190Z</v>
+        <v>2026-08-09T18:22:58.465Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -9732,7 +9732,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-09T18:19:36.205Z</v>
+        <v>2026-08-09T18:22:58.480Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -9749,10 +9749,10 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-09T18:19:36.221Z</v>
+        <v>2026-08-09T18:22:58.495Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -9769,10 +9769,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-09T18:19:36.237Z</v>
+        <v>2026-08-09T18:22:58.510Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -9789,10 +9789,10 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-09T18:19:36.253Z</v>
+        <v>2026-08-09T18:22:58.525Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -9812,7 +9812,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-09T18:19:36.269Z</v>
+        <v>2026-08-09T18:22:58.541Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -9832,7 +9832,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-09T18:19:36.285Z</v>
+        <v>2026-08-09T18:22:58.558Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -9849,10 +9849,10 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-09T18:19:36.301Z</v>
+        <v>2026-08-09T18:22:58.573Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -9872,7 +9872,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-09T18:19:36.317Z</v>
+        <v>2026-08-09T18:22:58.589Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -9889,10 +9889,10 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-09T18:19:36.333Z</v>
+        <v>2026-08-09T18:22:58.604Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -9912,7 +9912,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-09T18:19:36.347Z</v>
+        <v>2026-08-09T18:22:58.619Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -9932,7 +9932,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-09T18:19:36.364Z</v>
+        <v>2026-08-09T18:22:58.635Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -9949,10 +9949,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-09T18:19:36.379Z</v>
+        <v>2026-08-09T18:22:58.651Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -9969,10 +9969,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-09T18:19:36.394Z</v>
+        <v>2026-08-09T18:22:58.667Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -9989,10 +9989,10 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-09T18:19:36.411Z</v>
+        <v>2026-08-09T18:22:58.682Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -10012,7 +10012,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-09T18:19:36.424Z</v>
+        <v>2026-08-09T18:22:58.697Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -10029,10 +10029,10 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-09T18:19:36.440Z</v>
+        <v>2026-08-09T18:22:58.712Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -10049,10 +10049,10 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-09T18:19:36.455Z</v>
+        <v>2026-08-09T18:22:58.728Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -10072,7 +10072,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-09T18:19:36.471Z</v>
+        <v>2026-08-09T18:22:58.744Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -10089,10 +10089,10 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-09T18:19:36.487Z</v>
+        <v>2026-08-09T18:22:58.758Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -10112,7 +10112,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-09T18:19:36.502Z</v>
+        <v>2026-08-09T18:22:58.774Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -10132,7 +10132,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-09T18:19:36.517Z</v>
+        <v>2026-08-09T18:22:58.790Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -10149,10 +10149,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-09T18:19:36.533Z</v>
+        <v>2026-08-09T18:22:58.804Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -10172,7 +10172,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-09T18:19:36.548Z</v>
+        <v>2026-08-09T18:22:58.820Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -10192,7 +10192,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-09T18:19:36.563Z</v>
+        <v>2026-08-09T18:22:58.835Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -10209,10 +10209,10 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-09T18:19:36.579Z</v>
+        <v>2026-08-09T18:22:58.851Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -10232,7 +10232,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-09T18:19:36.594Z</v>
+        <v>2026-08-09T18:22:58.867Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -10252,7 +10252,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-09T18:19:36.609Z</v>
+        <v>2026-08-09T18:22:58.882Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -10272,7 +10272,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-09T18:19:36.625Z</v>
+        <v>2026-08-09T18:22:58.898Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -10289,10 +10289,10 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-09T18:19:36.641Z</v>
+        <v>2026-08-09T18:22:58.913Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -10312,7 +10312,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-09T18:19:36.656Z</v>
+        <v>2026-08-09T18:22:58.929Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -10332,7 +10332,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-09T18:19:36.671Z</v>
+        <v>2026-08-09T18:22:58.944Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -10352,7 +10352,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-09T18:19:36.687Z</v>
+        <v>2026-08-09T18:22:58.960Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -10369,10 +10369,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-09T18:19:36.702Z</v>
+        <v>2026-08-09T18:22:58.976Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -10389,10 +10389,10 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-09T18:19:36.717Z</v>
+        <v>2026-08-09T18:22:58.993Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -10412,7 +10412,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-09T18:19:36.733Z</v>
+        <v>2026-08-09T18:22:59.008Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -10432,7 +10432,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-09T18:19:36.748Z</v>
+        <v>2026-08-09T18:22:59.023Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -10449,10 +10449,10 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-09T18:19:36.764Z</v>
+        <v>2026-08-09T18:22:59.038Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -10469,10 +10469,10 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-09T18:19:36.778Z</v>
+        <v>2026-08-09T18:22:59.054Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -10489,10 +10489,10 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-09T18:19:36.794Z</v>
+        <v>2026-08-09T18:22:59.069Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -10512,7 +10512,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-09T18:19:36.809Z</v>
+        <v>2026-08-09T18:22:59.085Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -10532,7 +10532,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-09T18:19:36.825Z</v>
+        <v>2026-08-09T18:22:59.100Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -10549,10 +10549,10 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-09T18:19:36.840Z</v>
+        <v>2026-08-09T18:22:59.116Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -10569,10 +10569,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-09T18:19:36.856Z</v>
+        <v>2026-08-09T18:22:59.131Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -10592,7 +10592,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-09T18:19:36.872Z</v>
+        <v>2026-08-09T18:22:59.147Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -10609,10 +10609,10 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-09T18:19:36.887Z</v>
+        <v>2026-08-09T18:22:59.163Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -10629,10 +10629,10 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-09T18:19:36.904Z</v>
+        <v>2026-08-09T18:22:59.178Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -10649,10 +10649,10 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-09T18:19:36.919Z</v>
+        <v>2026-08-09T18:22:59.194Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -10669,10 +10669,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-09T18:19:36.934Z</v>
+        <v>2026-08-09T18:22:59.210Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -10692,7 +10692,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-09T18:19:36.949Z</v>
+        <v>2026-08-09T18:22:59.225Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -10709,10 +10709,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-09T18:19:36.966Z</v>
+        <v>2026-08-09T18:22:59.240Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -10732,7 +10732,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-09T18:19:36.979Z</v>
+        <v>2026-08-09T18:22:59.255Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -10752,7 +10752,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-09T18:19:36.995Z</v>
+        <v>2026-08-09T18:22:59.271Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -10772,7 +10772,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-09T18:19:37.012Z</v>
+        <v>2026-08-09T18:22:59.288Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -10792,7 +10792,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-09T18:19:37.026Z</v>
+        <v>2026-08-09T18:22:59.303Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -10809,10 +10809,10 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-09T18:19:37.042Z</v>
+        <v>2026-08-09T18:22:59.318Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -10829,10 +10829,10 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-09T18:19:37.058Z</v>
+        <v>2026-08-09T18:22:59.333Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -10849,10 +10849,10 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-09T18:19:37.073Z</v>
+        <v>2026-08-09T18:22:59.349Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -10872,7 +10872,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-09T18:19:37.089Z</v>
+        <v>2026-08-09T18:22:59.365Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -10892,7 +10892,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-09T18:19:37.104Z</v>
+        <v>2026-08-09T18:22:59.380Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -10912,7 +10912,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-09T18:19:37.119Z</v>
+        <v>2026-08-09T18:22:59.396Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -10929,10 +10929,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-09T18:19:37.134Z</v>
+        <v>2026-08-09T18:22:59.412Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -10949,10 +10949,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-09T18:19:37.149Z</v>
+        <v>2026-08-09T18:22:59.428Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -10972,7 +10972,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-09T18:19:37.164Z</v>
+        <v>2026-08-09T18:22:59.443Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -10992,7 +10992,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-09T18:19:37.181Z</v>
+        <v>2026-08-09T18:22:59.459Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -11009,10 +11009,10 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-09T18:19:37.196Z</v>
+        <v>2026-08-09T18:22:59.475Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -11029,10 +11029,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-09T18:19:37.211Z</v>
+        <v>2026-08-09T18:22:59.491Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -11049,10 +11049,10 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-09T18:19:37.227Z</v>
+        <v>2026-08-09T18:22:59.506Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -11069,10 +11069,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-09T18:19:37.243Z</v>
+        <v>2026-08-09T18:22:59.521Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -11089,10 +11089,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-09T18:19:37.258Z</v>
+        <v>2026-08-09T18:22:59.537Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -11109,10 +11109,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-09T18:19:37.275Z</v>
+        <v>2026-08-09T18:22:59.553Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -11129,10 +11129,10 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-09T18:19:37.291Z</v>
+        <v>2026-08-09T18:22:59.568Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -11149,10 +11149,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-09T18:19:37.306Z</v>
+        <v>2026-08-09T18:22:59.584Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -11172,7 +11172,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-09T18:19:37.321Z</v>
+        <v>2026-08-09T18:22:59.599Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -11189,10 +11189,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-09T18:19:37.336Z</v>
+        <v>2026-08-09T18:22:59.615Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -11209,10 +11209,10 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-09T18:19:37.351Z</v>
+        <v>2026-08-09T18:22:59.631Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -11232,7 +11232,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-09T18:19:37.367Z</v>
+        <v>2026-08-09T18:22:59.647Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -11249,10 +11249,10 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-09T18:19:37.382Z</v>
+        <v>2026-08-09T18:22:59.663Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -11269,10 +11269,10 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-09T18:19:37.398Z</v>
+        <v>2026-08-09T18:22:59.678Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -11289,10 +11289,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-09T18:19:37.413Z</v>
+        <v>2026-08-09T18:22:59.694Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -11309,10 +11309,10 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-09T18:19:37.428Z</v>
+        <v>2026-08-09T18:22:59.711Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -11329,10 +11329,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-09T18:19:37.444Z</v>
+        <v>2026-08-09T18:22:59.726Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -11352,7 +11352,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-09T18:19:37.458Z</v>
+        <v>2026-08-09T18:22:59.741Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -11369,10 +11369,10 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-09T18:19:37.474Z</v>
+        <v>2026-08-09T18:22:59.756Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -11392,7 +11392,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-09T18:19:37.491Z</v>
+        <v>2026-08-09T18:22:59.772Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -11412,7 +11412,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-09T18:19:37.505Z</v>
+        <v>2026-08-09T18:22:59.787Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -11429,10 +11429,10 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-09T18:19:37.521Z</v>
+        <v>2026-08-09T18:22:59.802Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -11449,10 +11449,10 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-09T18:19:37.536Z</v>
+        <v>2026-08-09T18:22:59.818Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -11472,7 +11472,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-09T18:19:37.552Z</v>
+        <v>2026-08-09T18:22:59.834Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -11489,10 +11489,10 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-09T18:19:37.568Z</v>
+        <v>2026-08-09T18:22:59.849Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -11509,10 +11509,10 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-09T18:19:37.583Z</v>
+        <v>2026-08-09T18:22:59.866Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -11529,10 +11529,10 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-09T18:19:37.599Z</v>
+        <v>2026-08-09T18:22:59.881Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -11549,10 +11549,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-09T18:19:37.614Z</v>
+        <v>2026-08-09T18:22:59.897Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -11569,10 +11569,10 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-09T18:19:37.629Z</v>
+        <v>2026-08-09T18:22:59.913Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -11592,7 +11592,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-09T18:19:37.644Z</v>
+        <v>2026-08-09T18:22:59.928Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -11612,7 +11612,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-09T18:19:37.661Z</v>
+        <v>2026-08-09T18:22:59.945Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -11629,10 +11629,10 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-09T18:19:37.676Z</v>
+        <v>2026-08-09T18:22:59.961Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -11652,7 +11652,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-09T18:19:37.692Z</v>
+        <v>2026-08-09T18:22:59.977Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -11672,7 +11672,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-09T18:19:37.708Z</v>
+        <v>2026-08-09T18:22:59.993Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -11689,10 +11689,10 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-09T18:19:37.723Z</v>
+        <v>2026-08-09T18:23:00.009Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -11709,10 +11709,10 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-09T18:19:37.739Z</v>
+        <v>2026-08-09T18:23:00.025Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -11729,10 +11729,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-09T18:19:37.754Z</v>
+        <v>2026-08-09T18:23:00.041Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -11752,7 +11752,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-09T18:19:37.769Z</v>
+        <v>2026-08-09T18:23:00.056Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -11769,10 +11769,10 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-09T18:19:37.785Z</v>
+        <v>2026-08-09T18:23:00.071Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -11792,7 +11792,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-09T18:19:37.801Z</v>
+        <v>2026-08-09T18:23:00.087Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -11812,7 +11812,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-09T18:19:37.817Z</v>
+        <v>2026-08-09T18:23:00.103Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -11829,10 +11829,10 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-09T18:19:37.832Z</v>
+        <v>2026-08-09T18:23:00.119Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -11852,7 +11852,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-09T18:19:37.848Z</v>
+        <v>2026-08-09T18:23:00.135Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -11869,10 +11869,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-09T18:19:37.863Z</v>
+        <v>2026-08-09T18:23:00.151Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -11889,10 +11889,10 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-09T18:19:37.879Z</v>
+        <v>2026-08-09T18:23:00.166Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -11909,10 +11909,10 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-09T18:19:37.896Z</v>
+        <v>2026-08-09T18:23:00.180Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -11929,10 +11929,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-09T18:19:37.911Z</v>
+        <v>2026-08-09T18:23:00.197Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -11952,7 +11952,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-09T18:19:37.927Z</v>
+        <v>2026-08-09T18:23:00.213Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -11972,7 +11972,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-09T18:19:37.941Z</v>
+        <v>2026-08-09T18:23:00.228Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -11989,10 +11989,10 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-09T18:19:37.957Z</v>
+        <v>2026-08-09T18:23:00.243Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -12012,7 +12012,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-09T18:19:37.972Z</v>
+        <v>2026-08-09T18:23:00.258Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -12029,10 +12029,10 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-09T18:19:37.987Z</v>
+        <v>2026-08-09T18:23:00.274Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -12052,7 +12052,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-09T18:19:38.002Z</v>
+        <v>2026-08-09T18:23:00.289Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -12069,10 +12069,10 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-09T18:19:38.018Z</v>
+        <v>2026-08-09T18:23:00.304Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -12092,7 +12092,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-09T18:19:38.034Z</v>
+        <v>2026-08-09T18:23:00.320Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -12112,7 +12112,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-09T18:19:38.050Z</v>
+        <v>2026-08-09T18:23:00.336Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -12132,7 +12132,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-09T18:19:38.066Z</v>
+        <v>2026-08-09T18:23:00.352Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -12152,7 +12152,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-09T18:19:38.081Z</v>
+        <v>2026-08-09T18:23:00.366Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -12172,7 +12172,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-09T18:19:38.097Z</v>
+        <v>2026-08-09T18:23:00.383Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -12192,7 +12192,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-09T18:19:38.112Z</v>
+        <v>2026-08-09T18:23:00.398Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -12209,10 +12209,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-09T18:19:38.128Z</v>
+        <v>2026-08-09T18:23:00.413Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -12232,7 +12232,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-09T18:19:38.143Z</v>
+        <v>2026-08-09T18:23:00.428Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -12249,10 +12249,10 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-09T18:19:38.159Z</v>
+        <v>2026-08-09T18:23:00.443Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -12272,7 +12272,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-09T18:19:38.177Z</v>
+        <v>2026-08-09T18:23:00.459Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -12289,10 +12289,10 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-09T18:19:38.190Z</v>
+        <v>2026-08-09T18:23:00.475Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -12312,7 +12312,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-09T18:19:38.205Z</v>
+        <v>2026-08-09T18:23:00.491Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -12332,7 +12332,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-09T18:19:38.221Z</v>
+        <v>2026-08-09T18:23:00.507Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -12349,10 +12349,10 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>0.02 sec</v>
+        <v>0.03 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-09T18:19:38.237Z</v>
+        <v>2026-08-09T18:23:00.537Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -12369,10 +12369,10 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-09T18:19:38.252Z</v>
+        <v>2026-08-09T18:23:00.556Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -12389,10 +12389,10 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-09T18:19:38.267Z</v>
+        <v>2026-08-09T18:23:00.572Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -12412,7 +12412,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-09T18:19:38.283Z</v>
+        <v>2026-08-09T18:23:00.588Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -12429,10 +12429,10 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-09T18:19:38.299Z</v>
+        <v>2026-08-09T18:23:00.600Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -12449,10 +12449,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-09T18:19:38.314Z</v>
+        <v>2026-08-09T18:23:00.616Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -12472,7 +12472,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-09T18:19:38.330Z</v>
+        <v>2026-08-09T18:23:00.632Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -12492,7 +12492,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-09T18:19:38.346Z</v>
+        <v>2026-08-09T18:23:00.648Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -12509,10 +12509,10 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-09T18:19:38.363Z</v>
+        <v>2026-08-09T18:23:00.664Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -12529,10 +12529,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-09T18:19:38.377Z</v>
+        <v>2026-08-09T18:23:00.680Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -12549,10 +12549,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-09T18:19:38.395Z</v>
+        <v>2026-08-09T18:23:00.696Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -12572,7 +12572,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-09T18:19:38.409Z</v>
+        <v>2026-08-09T18:23:00.711Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -12592,7 +12592,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-09T18:19:38.423Z</v>
+        <v>2026-08-09T18:23:00.726Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -12612,7 +12612,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-09T18:19:38.438Z</v>
+        <v>2026-08-09T18:23:00.741Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -12629,10 +12629,10 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-09T18:19:38.453Z</v>
+        <v>2026-08-09T18:23:00.757Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -12649,10 +12649,10 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-09T18:19:38.469Z</v>
+        <v>2026-08-09T18:23:00.772Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -12672,7 +12672,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-09T18:19:38.485Z</v>
+        <v>2026-08-09T18:23:00.789Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -12692,7 +12692,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-09T18:19:38.500Z</v>
+        <v>2026-08-09T18:23:00.804Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -12712,7 +12712,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-09T18:19:38.515Z</v>
+        <v>2026-08-09T18:23:00.820Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -12732,7 +12732,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-09T18:19:38.531Z</v>
+        <v>2026-08-09T18:23:00.836Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -12749,10 +12749,10 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-09T18:19:38.547Z</v>
+        <v>2026-08-09T18:23:00.851Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -12769,10 +12769,10 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-09T18:19:38.562Z</v>
+        <v>2026-08-09T18:23:00.867Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -12792,7 +12792,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-09T18:19:38.578Z</v>
+        <v>2026-08-09T18:23:00.883Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -12809,10 +12809,10 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-09T18:19:38.595Z</v>
+        <v>2026-08-09T18:23:00.898Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -12832,7 +12832,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-09T18:19:38.609Z</v>
+        <v>2026-08-09T18:23:00.913Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -12849,10 +12849,10 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-09T18:19:38.624Z</v>
+        <v>2026-08-09T18:23:00.929Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -12869,10 +12869,10 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-09T18:19:38.639Z</v>
+        <v>2026-08-09T18:23:00.945Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -12889,10 +12889,10 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-09T18:19:38.654Z</v>
+        <v>2026-08-09T18:23:00.961Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -12909,10 +12909,10 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-09T18:19:38.669Z</v>
+        <v>2026-08-09T18:23:00.978Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -12929,10 +12929,10 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-09T18:19:38.685Z</v>
+        <v>2026-08-09T18:23:00.993Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -12952,7 +12952,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-09T18:19:38.701Z</v>
+        <v>2026-08-09T18:23:01.009Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -12969,10 +12969,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-09T18:19:38.715Z</v>
+        <v>2026-08-09T18:23:01.025Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -12992,7 +12992,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-09T18:19:38.731Z</v>
+        <v>2026-08-09T18:23:01.041Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -13009,10 +13009,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-09T18:19:38.746Z</v>
+        <v>2026-08-09T18:23:01.057Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -13032,7 +13032,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-09T18:19:38.762Z</v>
+        <v>2026-08-09T18:23:01.073Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -13049,10 +13049,10 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-09T18:19:38.777Z</v>
+        <v>2026-08-09T18:23:01.089Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -13069,10 +13069,10 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-09T18:19:38.794Z</v>
+        <v>2026-08-09T18:23:01.104Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -13089,10 +13089,10 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-09T18:19:38.810Z</v>
+        <v>2026-08-09T18:23:01.119Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -13109,10 +13109,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-09T18:19:38.826Z</v>
+        <v>2026-08-09T18:23:01.136Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -13132,7 +13132,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-09T18:19:38.841Z</v>
+        <v>2026-08-09T18:23:01.151Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -13152,7 +13152,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-09T18:19:38.856Z</v>
+        <v>2026-08-09T18:23:01.166Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -13172,7 +13172,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-09T18:19:38.872Z</v>
+        <v>2026-08-09T18:23:01.182Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -13189,10 +13189,10 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-09T18:19:38.888Z</v>
+        <v>2026-08-09T18:23:01.197Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -13212,7 +13212,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-09T18:19:38.903Z</v>
+        <v>2026-08-09T18:23:01.212Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -13232,7 +13232,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-09T18:19:38.919Z</v>
+        <v>2026-08-09T18:23:01.228Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -13249,10 +13249,10 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-09T18:19:38.935Z</v>
+        <v>2026-08-09T18:23:01.242Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -13272,7 +13272,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-09T18:19:38.951Z</v>
+        <v>2026-08-09T18:23:01.258Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -13292,7 +13292,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-09T18:19:38.965Z</v>
+        <v>2026-08-09T18:23:01.273Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -13312,7 +13312,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-09T18:19:38.981Z</v>
+        <v>2026-08-09T18:23:01.290Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -13329,10 +13329,10 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-09T18:19:38.997Z</v>
+        <v>2026-08-09T18:23:01.304Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -13349,10 +13349,10 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-09T18:19:39.012Z</v>
+        <v>2026-08-09T18:23:01.320Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -13372,7 +13372,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-09T18:19:39.029Z</v>
+        <v>2026-08-09T18:23:01.336Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -13392,7 +13392,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-09T18:19:39.045Z</v>
+        <v>2026-08-09T18:23:01.352Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -13412,7 +13412,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-09T18:19:39.059Z</v>
+        <v>2026-08-09T18:23:01.366Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -13432,7 +13432,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-09T18:19:39.076Z</v>
+        <v>2026-08-09T18:23:01.382Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -13452,7 +13452,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-09T18:19:39.091Z</v>
+        <v>2026-08-09T18:23:01.397Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -13472,7 +13472,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-09T18:19:39.107Z</v>
+        <v>2026-08-09T18:23:01.413Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -13492,7 +13492,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-09T18:19:39.122Z</v>
+        <v>2026-08-09T18:23:01.428Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -13512,7 +13512,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-09T18:19:39.137Z</v>
+        <v>2026-08-09T18:23:01.444Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -13529,10 +13529,10 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-09T18:19:39.153Z</v>
+        <v>2026-08-09T18:23:01.459Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -13552,7 +13552,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-09T18:19:39.169Z</v>
+        <v>2026-08-09T18:23:01.476Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -13572,7 +13572,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-09T18:19:39.184Z</v>
+        <v>2026-08-09T18:23:01.490Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -13589,10 +13589,10 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-09T18:19:39.199Z</v>
+        <v>2026-08-09T18:23:01.507Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -13609,10 +13609,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-09T18:19:39.215Z</v>
+        <v>2026-08-09T18:23:01.522Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -13629,10 +13629,10 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-09T18:19:39.231Z</v>
+        <v>2026-08-09T18:23:01.537Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -13649,10 +13649,10 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-09T18:19:39.247Z</v>
+        <v>2026-08-09T18:23:01.552Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -13669,10 +13669,10 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-09T18:19:39.263Z</v>
+        <v>2026-08-09T18:23:01.567Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -13689,10 +13689,10 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-09T18:19:39.279Z</v>
+        <v>2026-08-09T18:23:01.582Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -13712,7 +13712,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-09T18:19:39.294Z</v>
+        <v>2026-08-09T18:23:01.598Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -13729,10 +13729,10 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-09T18:19:39.309Z</v>
+        <v>2026-08-09T18:23:01.614Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -13752,7 +13752,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-09T18:19:39.324Z</v>
+        <v>2026-08-09T18:23:01.629Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -13772,7 +13772,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-09T18:19:39.339Z</v>
+        <v>2026-08-09T18:23:01.644Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -13792,7 +13792,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-09T18:19:39.355Z</v>
+        <v>2026-08-09T18:23:01.661Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -13809,10 +13809,10 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-09T18:19:39.371Z</v>
+        <v>2026-08-09T18:23:01.677Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -13832,7 +13832,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-09T18:19:39.385Z</v>
+        <v>2026-08-09T18:23:01.692Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -13849,10 +13849,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-09T18:19:39.400Z</v>
+        <v>2026-08-09T18:23:01.709Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -13869,10 +13869,10 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-09T18:19:39.416Z</v>
+        <v>2026-08-09T18:23:01.723Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -13892,7 +13892,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-09T18:19:39.432Z</v>
+        <v>2026-08-09T18:23:01.740Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -13909,10 +13909,10 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-09T18:19:39.448Z</v>
+        <v>2026-08-09T18:23:01.755Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -13929,10 +13929,10 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-09T18:19:39.462Z</v>
+        <v>2026-08-09T18:23:01.771Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -13949,10 +13949,10 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-09T18:19:39.478Z</v>
+        <v>2026-08-09T18:23:01.785Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -13969,10 +13969,10 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-09T18:19:39.495Z</v>
+        <v>2026-08-09T18:23:01.801Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -13992,7 +13992,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-09T18:19:39.510Z</v>
+        <v>2026-08-09T18:23:01.816Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -14009,10 +14009,10 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-09T18:19:39.525Z</v>
+        <v>2026-08-09T18:23:01.832Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -14029,10 +14029,10 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-09T18:19:39.541Z</v>
+        <v>2026-08-09T18:23:01.848Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -14052,7 +14052,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-09T18:19:39.555Z</v>
+        <v>2026-08-09T18:23:01.863Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -14072,7 +14072,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-09T18:19:39.570Z</v>
+        <v>2026-08-09T18:23:01.878Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -14092,7 +14092,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-09T18:19:39.587Z</v>
+        <v>2026-08-09T18:23:01.894Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -14109,10 +14109,10 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-09T18:19:39.601Z</v>
+        <v>2026-08-09T18:23:01.911Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -14129,10 +14129,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-09T18:19:39.618Z</v>
+        <v>2026-08-09T18:23:01.926Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -14149,10 +14149,10 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-09T18:19:39.633Z</v>
+        <v>2026-08-09T18:23:01.942Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -14169,10 +14169,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-09T18:19:39.649Z</v>
+        <v>2026-08-09T18:23:01.957Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -14189,10 +14189,10 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-09T18:19:39.665Z</v>
+        <v>2026-08-09T18:23:01.972Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -14212,7 +14212,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-09T18:19:39.681Z</v>
+        <v>2026-08-09T18:23:01.988Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -14229,10 +14229,10 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-09T18:19:39.696Z</v>
+        <v>2026-08-09T18:23:02.004Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -14249,10 +14249,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-09T18:19:39.712Z</v>
+        <v>2026-08-09T18:23:02.018Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -14269,10 +14269,10 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-09T18:19:39.727Z</v>
+        <v>2026-08-09T18:23:02.034Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -14289,10 +14289,10 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-09T18:19:39.742Z</v>
+        <v>2026-08-09T18:23:02.050Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -14312,7 +14312,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-09T18:19:39.757Z</v>
+        <v>2026-08-09T18:23:02.065Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -14329,10 +14329,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-09T18:19:39.774Z</v>
+        <v>2026-08-09T18:23:02.080Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -14349,10 +14349,10 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-09T18:19:39.788Z</v>
+        <v>2026-08-09T18:23:02.096Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -14369,10 +14369,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-09T18:19:39.803Z</v>
+        <v>2026-08-09T18:23:02.112Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -14392,7 +14392,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-09T18:19:39.819Z</v>
+        <v>2026-08-09T18:23:02.128Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -14409,10 +14409,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-09T18:19:39.835Z</v>
+        <v>2026-08-09T18:23:02.143Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -14432,7 +14432,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-09T18:19:39.850Z</v>
+        <v>2026-08-09T18:23:02.158Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -14452,7 +14452,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-09T18:19:39.866Z</v>
+        <v>2026-08-09T18:23:02.174Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -14469,10 +14469,10 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-09T18:19:39.882Z</v>
+        <v>2026-08-09T18:23:02.189Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -14489,10 +14489,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-09T18:19:39.897Z</v>
+        <v>2026-08-09T18:23:02.205Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -14509,10 +14509,10 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-09T18:19:39.914Z</v>
+        <v>2026-08-09T18:23:02.221Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -14529,10 +14529,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-09T18:19:39.930Z</v>
+        <v>2026-08-09T18:23:02.237Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -14549,10 +14549,10 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-09T18:19:39.944Z</v>
+        <v>2026-08-09T18:23:02.253Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -14569,10 +14569,10 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-09T18:19:39.960Z</v>
+        <v>2026-08-09T18:23:02.268Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -14589,10 +14589,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-09T18:19:39.976Z</v>
+        <v>2026-08-09T18:23:02.284Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -14612,7 +14612,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-09T18:19:39.991Z</v>
+        <v>2026-08-09T18:23:02.298Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -14632,7 +14632,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-09T18:19:40.007Z</v>
+        <v>2026-08-09T18:23:02.314Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -14652,7 +14652,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-09T18:19:40.022Z</v>
+        <v>2026-08-09T18:23:02.329Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -14669,10 +14669,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-09T18:19:40.037Z</v>
+        <v>2026-08-09T18:23:02.345Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -14689,10 +14689,10 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-09T18:19:40.053Z</v>
+        <v>2026-08-09T18:23:02.360Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -14712,7 +14712,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-09T18:19:40.068Z</v>
+        <v>2026-08-09T18:23:02.376Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -14729,10 +14729,10 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-09T18:19:40.084Z</v>
+        <v>2026-08-09T18:23:02.391Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -14749,10 +14749,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-09T18:19:40.099Z</v>
+        <v>2026-08-09T18:23:02.407Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -14772,7 +14772,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-09T18:19:40.115Z</v>
+        <v>2026-08-09T18:23:02.424Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -14792,7 +14792,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-09T18:19:40.131Z</v>
+        <v>2026-08-09T18:23:02.439Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -14809,10 +14809,10 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-09T18:19:40.147Z</v>
+        <v>2026-08-09T18:23:02.454Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -14829,10 +14829,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-09T18:19:40.162Z</v>
+        <v>2026-08-09T18:23:02.470Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -14849,10 +14849,10 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-09T18:19:40.178Z</v>
+        <v>2026-08-09T18:23:02.485Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -14872,7 +14872,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-09T18:19:40.195Z</v>
+        <v>2026-08-09T18:23:02.501Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -14889,10 +14889,10 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-09T18:19:40.211Z</v>
+        <v>2026-08-09T18:23:02.516Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -14912,7 +14912,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-09T18:19:40.226Z</v>
+        <v>2026-08-09T18:23:02.531Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -14929,10 +14929,10 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-09T18:19:40.241Z</v>
+        <v>2026-08-09T18:23:02.547Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -14949,10 +14949,10 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-09T18:19:40.256Z</v>
+        <v>2026-08-09T18:23:02.563Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -14969,10 +14969,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-09T18:19:40.273Z</v>
+        <v>2026-08-09T18:23:02.578Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -14989,10 +14989,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-09T18:19:40.288Z</v>
+        <v>2026-08-09T18:23:02.594Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -15012,7 +15012,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-09T18:19:40.303Z</v>
+        <v>2026-08-09T18:23:02.609Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -15029,10 +15029,10 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-09T18:19:40.319Z</v>
+        <v>2026-08-09T18:23:02.624Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -15049,10 +15049,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-09T18:19:40.334Z</v>
+        <v>2026-08-09T18:23:02.640Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -15072,7 +15072,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-09T18:19:40.349Z</v>
+        <v>2026-08-09T18:23:02.655Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -15092,7 +15092,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-09T18:19:40.365Z</v>
+        <v>2026-08-09T18:23:02.671Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -15112,7 +15112,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-09T18:19:40.382Z</v>
+        <v>2026-08-09T18:23:02.687Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -15132,7 +15132,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-09T18:19:40.396Z</v>
+        <v>2026-08-09T18:23:02.702Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -15152,7 +15152,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-09T18:19:40.412Z</v>
+        <v>2026-08-09T18:23:02.718Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -15172,7 +15172,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-09T18:19:40.427Z</v>
+        <v>2026-08-09T18:23:02.733Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -15192,7 +15192,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-09T18:19:40.444Z</v>
+        <v>2026-08-09T18:23:02.749Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -15209,10 +15209,10 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-09T18:19:40.460Z</v>
+        <v>2026-08-09T18:23:02.764Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -15229,10 +15229,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-09T18:19:40.476Z</v>
+        <v>2026-08-09T18:23:02.779Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -15252,7 +15252,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-09T18:19:40.490Z</v>
+        <v>2026-08-09T18:23:02.794Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -15269,10 +15269,10 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-09T18:19:40.505Z</v>
+        <v>2026-08-09T18:23:02.810Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -15292,7 +15292,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-09T18:19:40.520Z</v>
+        <v>2026-08-09T18:23:02.825Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -15312,7 +15312,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-09T18:19:40.535Z</v>
+        <v>2026-08-09T18:23:02.840Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -15332,7 +15332,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-09T18:19:40.551Z</v>
+        <v>2026-08-09T18:23:02.856Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -15349,10 +15349,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-09T18:19:40.567Z</v>
+        <v>2026-08-09T18:23:02.871Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -15372,7 +15372,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-09T18:19:40.583Z</v>
+        <v>2026-08-09T18:23:02.887Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -15392,7 +15392,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-09T18:19:40.598Z</v>
+        <v>2026-08-09T18:23:02.902Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -15409,10 +15409,10 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-09T18:19:40.614Z</v>
+        <v>2026-08-09T18:23:02.917Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -15432,7 +15432,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-09T18:19:40.629Z</v>
+        <v>2026-08-09T18:23:02.932Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -15452,7 +15452,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-09T18:19:40.645Z</v>
+        <v>2026-08-09T18:23:02.948Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -15469,10 +15469,10 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-09T18:19:40.660Z</v>
+        <v>2026-08-09T18:23:02.964Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -15492,7 +15492,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-09T18:19:40.676Z</v>
+        <v>2026-08-09T18:23:02.980Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -15512,7 +15512,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-09T18:19:40.691Z</v>
+        <v>2026-08-09T18:23:02.995Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -15529,10 +15529,10 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-09T18:19:40.707Z</v>
+        <v>2026-08-09T18:23:03.010Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -15549,10 +15549,10 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-09T18:19:40.722Z</v>
+        <v>2026-08-09T18:23:03.026Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -15569,10 +15569,10 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-09T18:19:40.737Z</v>
+        <v>2026-08-09T18:23:03.042Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -15589,10 +15589,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-09T18:19:40.753Z</v>
+        <v>2026-08-09T18:23:03.057Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -15612,7 +15612,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-09T18:19:40.768Z</v>
+        <v>2026-08-09T18:23:03.073Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -15632,7 +15632,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-09T18:19:40.784Z</v>
+        <v>2026-08-09T18:23:03.088Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -15649,10 +15649,10 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-09T18:19:40.799Z</v>
+        <v>2026-08-09T18:23:03.104Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -15669,10 +15669,10 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-09T18:19:40.815Z</v>
+        <v>2026-08-09T18:23:03.119Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -15689,10 +15689,10 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-09T18:19:40.830Z</v>
+        <v>2026-08-09T18:23:03.135Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -15712,7 +15712,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-09T18:19:40.846Z</v>
+        <v>2026-08-09T18:23:03.151Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -15729,10 +15729,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-09T18:19:40.862Z</v>
+        <v>2026-08-09T18:23:03.166Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -15749,10 +15749,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-09T18:19:40.877Z</v>
+        <v>2026-08-09T18:23:03.184Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -15769,10 +15769,10 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-09T18:19:40.893Z</v>
+        <v>2026-08-09T18:23:03.198Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -15789,10 +15789,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-09T18:19:40.908Z</v>
+        <v>2026-08-09T18:23:03.214Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -15812,7 +15812,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-09T18:19:40.923Z</v>
+        <v>2026-08-09T18:23:03.228Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -15829,10 +15829,10 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-09T18:19:40.938Z</v>
+        <v>2026-08-09T18:23:03.244Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -15852,7 +15852,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-09T18:19:40.954Z</v>
+        <v>2026-08-09T18:23:03.260Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -15869,10 +15869,10 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-09T18:19:40.970Z</v>
+        <v>2026-08-09T18:23:03.275Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -15889,10 +15889,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-09T18:19:40.984Z</v>
+        <v>2026-08-09T18:23:03.292Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -15912,7 +15912,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-09T18:19:41.000Z</v>
+        <v>2026-08-09T18:23:03.306Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -15929,10 +15929,10 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-09T18:19:41.015Z</v>
+        <v>2026-08-09T18:23:03.322Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -15952,7 +15952,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-09T18:19:41.031Z</v>
+        <v>2026-08-09T18:23:03.338Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -15969,10 +15969,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-09T18:19:41.047Z</v>
+        <v>2026-08-09T18:23:03.352Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -15992,7 +15992,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-09T18:19:41.063Z</v>
+        <v>2026-08-09T18:23:03.368Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -16012,7 +16012,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-09T18:19:41.079Z</v>
+        <v>2026-08-09T18:23:03.384Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -16032,7 +16032,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-09T18:19:41.094Z</v>
+        <v>2026-08-09T18:23:03.399Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -16049,10 +16049,10 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-09T18:19:41.110Z</v>
+        <v>2026-08-09T18:23:03.413Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -16072,7 +16072,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-09T18:19:41.125Z</v>
+        <v>2026-08-09T18:23:03.429Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -16089,10 +16089,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-09T18:19:41.140Z</v>
+        <v>2026-08-09T18:23:03.445Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -16109,10 +16109,10 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-09T18:19:41.156Z</v>
+        <v>2026-08-09T18:23:03.461Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -16129,10 +16129,10 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-09T18:19:41.172Z</v>
+        <v>2026-08-09T18:23:03.476Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -16152,7 +16152,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-09T18:19:41.188Z</v>
+        <v>2026-08-09T18:23:03.492Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -16172,7 +16172,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-09T18:19:41.204Z</v>
+        <v>2026-08-09T18:23:03.508Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -16192,7 +16192,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-09T18:19:41.219Z</v>
+        <v>2026-08-09T18:23:03.524Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -16212,7 +16212,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-09T18:19:41.234Z</v>
+        <v>2026-08-09T18:23:03.539Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -16232,7 +16232,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-09T18:19:41.250Z</v>
+        <v>2026-08-09T18:23:03.555Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -16249,10 +16249,10 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-09T18:19:41.266Z</v>
+        <v>2026-08-09T18:23:03.570Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -16272,7 +16272,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-09T18:19:41.282Z</v>
+        <v>2026-08-09T18:23:03.586Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -16292,7 +16292,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-09T18:19:41.298Z</v>
+        <v>2026-08-09T18:23:03.601Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -16309,10 +16309,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-09T18:19:41.314Z</v>
+        <v>2026-08-09T18:23:03.617Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -16332,7 +16332,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-09T18:19:41.329Z</v>
+        <v>2026-08-09T18:23:03.633Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -16352,7 +16352,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-09T18:19:41.344Z</v>
+        <v>2026-08-09T18:23:03.648Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -16369,10 +16369,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-09T18:19:41.359Z</v>
+        <v>2026-08-09T18:23:03.664Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -16392,7 +16392,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-09T18:19:41.374Z</v>
+        <v>2026-08-09T18:23:03.678Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -16412,7 +16412,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-09T18:19:41.390Z</v>
+        <v>2026-08-09T18:23:03.694Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -16429,10 +16429,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-09T18:19:41.406Z</v>
+        <v>2026-08-09T18:23:03.709Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -16452,7 +16452,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-09T18:19:41.421Z</v>
+        <v>2026-08-09T18:23:03.724Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -16472,7 +16472,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-09T18:19:41.437Z</v>
+        <v>2026-08-09T18:23:03.740Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -16489,10 +16489,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-09T18:19:41.452Z</v>
+        <v>2026-08-09T18:23:03.756Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -16512,7 +16512,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-09T18:19:41.467Z</v>
+        <v>2026-08-09T18:23:03.771Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -16532,7 +16532,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-09T18:19:41.483Z</v>
+        <v>2026-08-09T18:23:03.787Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -16552,7 +16552,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-09T18:19:41.500Z</v>
+        <v>2026-08-09T18:23:03.803Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -16569,10 +16569,10 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-09T18:19:41.515Z</v>
+        <v>2026-08-09T18:23:03.819Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -16592,7 +16592,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-09T18:19:41.531Z</v>
+        <v>2026-08-09T18:23:03.835Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -16612,7 +16612,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-09T18:19:41.546Z</v>
+        <v>2026-08-09T18:23:03.850Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -16632,7 +16632,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-09T18:19:41.561Z</v>
+        <v>2026-08-09T18:23:03.864Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -16652,7 +16652,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-09T18:19:41.577Z</v>
+        <v>2026-08-09T18:23:03.880Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -16672,7 +16672,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-09T18:19:41.593Z</v>
+        <v>2026-08-09T18:23:03.896Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -16689,10 +16689,10 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-09T18:19:41.608Z</v>
+        <v>2026-08-09T18:23:03.912Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>
@@ -29659,7 +29659,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I3" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="4">
@@ -29717,7 +29717,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I5" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="6">
@@ -29775,7 +29775,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I7" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="8">
@@ -29833,7 +29833,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I9" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="10">
@@ -29891,7 +29891,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I11" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="12">
@@ -29949,7 +29949,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I13" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="14">
@@ -30007,7 +30007,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I15" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="16">
@@ -30065,7 +30065,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I17" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="18">
@@ -30123,7 +30123,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I19" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="20">
@@ -30181,7 +30181,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I21" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="22">
@@ -30239,7 +30239,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I23" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="24">
@@ -30297,7 +30297,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I25" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="26">
@@ -30355,7 +30355,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I27" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="28">
@@ -30413,7 +30413,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I29" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="30">
@@ -30471,7 +30471,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I31" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="32">
@@ -30529,7 +30529,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I33" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="34">
@@ -30587,7 +30587,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I35" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="36">
@@ -30645,7 +30645,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I37" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="38">
@@ -30703,7 +30703,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I39" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="40">
@@ -30761,7 +30761,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I41" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="42">
@@ -30819,7 +30819,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I43" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="44">
@@ -30877,7 +30877,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I45" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="46">
@@ -30935,7 +30935,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I47" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="48">
@@ -30993,7 +30993,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I49" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="50">
@@ -31051,7 +31051,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I51" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="52">
@@ -31109,7 +31109,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I53" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="54">
@@ -31167,7 +31167,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I55" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="56">
@@ -31225,7 +31225,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I57" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="58">
@@ -31283,7 +31283,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I59" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="60">
@@ -31341,7 +31341,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I61" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="62">
@@ -31399,7 +31399,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I63" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="64">
@@ -31457,7 +31457,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I65" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="66">
@@ -31515,7 +31515,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I67" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="68">
@@ -31573,7 +31573,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I69" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="70">
@@ -31631,7 +31631,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I71" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="72">
@@ -31689,7 +31689,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I73" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="74">
@@ -31747,7 +31747,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I75" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="76">
@@ -31805,7 +31805,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I77" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="78">
@@ -31863,7 +31863,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I79" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="80">
@@ -31921,7 +31921,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I81" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="82">
@@ -31979,7 +31979,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I83" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="84">
@@ -32037,7 +32037,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I85" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="86">
@@ -32095,7 +32095,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I87" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="88">
@@ -32153,7 +32153,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I89" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="90">
@@ -32211,7 +32211,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I91" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="92">
@@ -32269,7 +32269,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I93" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="94">
@@ -32327,7 +32327,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I95" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="96">
@@ -32385,7 +32385,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I97" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="98">
@@ -32443,7 +32443,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I99" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="100">
@@ -32501,7 +32501,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I101" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="102">
@@ -32559,7 +32559,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I103" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="104">
@@ -32617,7 +32617,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I105" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="106">
@@ -32675,7 +32675,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I107" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="108">
@@ -32733,7 +32733,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I109" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="110">
@@ -32791,7 +32791,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I111" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="112">
@@ -32849,7 +32849,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I113" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="114">
@@ -32907,7 +32907,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I115" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="116">
@@ -32965,7 +32965,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I117" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="118">
@@ -33023,7 +33023,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I119" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="120">
@@ -33081,7 +33081,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I121" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="122">
@@ -33139,7 +33139,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I123" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="124">
@@ -33197,7 +33197,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I125" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="126">
@@ -33255,7 +33255,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I127" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="128">
@@ -33313,7 +33313,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I129" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="130">
@@ -33371,7 +33371,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I131" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="132">
@@ -33429,7 +33429,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I133" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="134">
@@ -33487,7 +33487,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I135" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="136">
@@ -33545,7 +33545,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I137" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="138">
@@ -33603,7 +33603,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I139" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="140">
@@ -33661,7 +33661,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I141" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="142">
@@ -33719,7 +33719,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I143" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="144">
@@ -33777,7 +33777,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I145" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="146">
@@ -33835,7 +33835,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I147" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="148">
@@ -33893,7 +33893,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I149" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="150">
@@ -33951,7 +33951,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I151" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="152">
@@ -34009,7 +34009,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I153" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="154">
@@ -34067,7 +34067,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I155" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="156">
@@ -34125,7 +34125,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I157" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="158">
@@ -34183,7 +34183,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I159" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="160">
@@ -34241,7 +34241,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I161" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="162">
@@ -34299,7 +34299,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I163" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="164">
@@ -34357,7 +34357,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I165" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="166">
@@ -34415,7 +34415,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I167" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="168">
@@ -34473,7 +34473,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I169" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="170">
@@ -34531,7 +34531,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I171" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="172">
@@ -34589,7 +34589,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I173" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="174">
@@ -34647,7 +34647,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I175" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="176">
@@ -34705,7 +34705,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I177" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="178">
@@ -34763,7 +34763,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I179" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="180">
@@ -34821,7 +34821,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I181" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="182">
@@ -34879,7 +34879,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I183" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="184">
@@ -34937,7 +34937,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I185" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="186">
@@ -34995,7 +34995,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I187" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="188">
@@ -35053,7 +35053,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I189" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="190">
@@ -35111,7 +35111,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I191" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="192">
@@ -35169,7 +35169,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I193" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="194">
@@ -35227,7 +35227,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I195" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="196">
@@ -35285,7 +35285,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I197" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="198">
@@ -35343,7 +35343,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I199" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="200">
@@ -35401,7 +35401,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I201" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="202">
@@ -35459,7 +35459,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I203" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="204">
@@ -35517,7 +35517,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I205" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="206">
@@ -35575,7 +35575,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I207" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="208">
@@ -35633,7 +35633,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I209" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="210">
@@ -35691,7 +35691,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I211" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="212">
@@ -35749,7 +35749,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I213" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="214">
@@ -35807,7 +35807,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I215" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="216">
@@ -35865,7 +35865,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I217" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="218">
@@ -35923,7 +35923,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I219" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="220">
@@ -35981,7 +35981,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I221" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="222">
@@ -36039,7 +36039,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I223" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="224">
@@ -36097,7 +36097,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I225" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="226">
@@ -36155,7 +36155,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I227" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="228">
@@ -36213,7 +36213,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I229" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="230">
@@ -36271,7 +36271,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I231" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="232">
@@ -36329,7 +36329,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I233" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="234">
@@ -36387,7 +36387,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I235" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="236">
@@ -36445,7 +36445,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I237" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="238">
@@ -36503,7 +36503,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I239" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="240">
@@ -36561,7 +36561,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I241" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="242">
@@ -36619,7 +36619,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I243" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="244">
@@ -36677,7 +36677,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I245" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="246">
@@ -36735,7 +36735,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I247" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="248">
@@ -36793,7 +36793,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I249" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="250">
@@ -36851,7 +36851,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I251" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="252">
@@ -36909,7 +36909,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I253" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="254">
@@ -36967,7 +36967,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I255" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="256">
@@ -37025,7 +37025,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I257" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="258">
@@ -37083,7 +37083,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I259" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="260">
@@ -37141,7 +37141,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I261" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="262">
@@ -37199,7 +37199,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I263" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="264">
@@ -37257,7 +37257,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I265" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="266">
@@ -37315,7 +37315,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I267" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="268">
@@ -37373,7 +37373,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I269" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="270">
@@ -37431,7 +37431,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I271" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="272">
@@ -37489,7 +37489,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I273" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="274">
@@ -37547,7 +37547,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I275" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="276">
@@ -37605,7 +37605,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I277" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="278">
@@ -37663,7 +37663,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I279" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="280">
@@ -37721,7 +37721,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I281" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="282">
@@ -37779,7 +37779,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I283" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="284">
@@ -37837,7 +37837,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I285" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="286">
@@ -37895,7 +37895,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I287" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="288">
@@ -37953,7 +37953,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I289" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="290">
@@ -38011,7 +38011,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I291" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="292">
@@ -38069,7 +38069,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I293" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="294">
@@ -38127,7 +38127,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I295" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="296">
@@ -38185,7 +38185,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I297" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="298">
@@ -38243,7 +38243,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I299" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="300">
@@ -38301,7 +38301,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I301" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="302">
@@ -38359,7 +38359,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I303" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="304">
@@ -38417,7 +38417,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I305" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="306">
@@ -38475,7 +38475,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I307" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="308">
@@ -38533,7 +38533,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I309" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="310">
@@ -38591,7 +38591,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I311" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="312">
@@ -38649,7 +38649,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I313" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="314">
@@ -38707,7 +38707,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I315" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="316">
@@ -38765,7 +38765,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I317" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="318">
@@ -38823,7 +38823,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I319" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="320">
@@ -38881,7 +38881,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I321" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="322">
@@ -38939,7 +38939,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I323" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="324">
@@ -38997,7 +38997,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I325" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="326">
@@ -39055,7 +39055,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I327" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="328">
@@ -39113,7 +39113,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I329" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="330">
@@ -39171,7 +39171,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I331" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="332">
@@ -39229,7 +39229,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I333" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="334">
@@ -39287,7 +39287,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I335" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="336">
@@ -39345,7 +39345,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I337" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="338">
@@ -39403,7 +39403,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I339" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="340">
@@ -39461,7 +39461,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I341" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="342">
@@ -39519,7 +39519,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I343" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="344">
@@ -39577,7 +39577,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I345" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="346">
@@ -39635,7 +39635,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I347" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="348">
@@ -39693,7 +39693,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I349" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="350">
@@ -39751,7 +39751,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I351" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="352">
@@ -39809,7 +39809,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I353" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="354">
@@ -39867,7 +39867,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I355" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="356">
@@ -39925,7 +39925,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I357" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="358">
@@ -39983,7 +39983,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I359" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="360">
@@ -40041,7 +40041,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I361" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="362">
@@ -40099,7 +40099,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I363" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="364">
@@ -40157,7 +40157,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I365" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="366">
@@ -40215,7 +40215,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I367" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="368">
@@ -40273,7 +40273,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I369" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="370">
@@ -40331,7 +40331,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I371" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="372">
@@ -40389,7 +40389,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I373" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="374">
@@ -40447,7 +40447,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I375" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="376">
@@ -40505,7 +40505,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I377" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="378">
@@ -40563,7 +40563,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I379" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="380">
@@ -40621,7 +40621,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I381" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="382">
@@ -40679,7 +40679,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I383" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="384">
@@ -40737,7 +40737,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I385" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="386">
@@ -40795,7 +40795,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I387" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="388">
@@ -40853,7 +40853,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I389" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="390">
@@ -40911,7 +40911,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I391" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="392">
@@ -40969,7 +40969,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I393" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="394">
@@ -41027,7 +41027,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I395" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="396">
@@ -41085,7 +41085,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I397" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="398">
@@ -41143,7 +41143,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I399" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="400">
@@ -41201,7 +41201,7 @@
         <v>Maintain current implementation and monitor for future issues.</v>
       </c>
       <c r="I401" t="str">
-        <v>NOT APPLICABLE</v>
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
